--- a/research/traditional_assets/database/data/pakistan/pakistan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ24"/>
+  <dimension ref="A1:AQ23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0504</v>
+        <v>0.00176</v>
       </c>
       <c r="E2">
-        <v>0.00643</v>
+        <v>0.07625</v>
       </c>
       <c r="G2">
-        <v>0.2570861767973338</v>
+        <v>0.3159206275957545</v>
       </c>
       <c r="H2">
-        <v>0.2540707824154896</v>
+        <v>0.3132441162898015</v>
       </c>
       <c r="I2">
-        <v>0.2157752737660689</v>
+        <v>0.2963728657129672</v>
       </c>
       <c r="J2">
-        <v>0.181237943085816</v>
+        <v>0.2361372133158393</v>
       </c>
       <c r="K2">
-        <v>15.835</v>
+        <v>11.959</v>
       </c>
       <c r="L2">
-        <v>0.2513093159815902</v>
+        <v>0.2207475772958006</v>
       </c>
       <c r="M2">
-        <v>7.9902</v>
+        <v>6.4636</v>
       </c>
       <c r="N2">
-        <v>0.06478610579573833</v>
+        <v>0.09511308621628384</v>
       </c>
       <c r="O2">
-        <v>0.5045910956741395</v>
+        <v>0.5404799732419099</v>
       </c>
       <c r="P2">
-        <v>7.9902</v>
+        <v>6.4636</v>
       </c>
       <c r="Q2">
-        <v>0.06478610579573833</v>
+        <v>0.09511308621628384</v>
       </c>
       <c r="R2">
-        <v>0.5045910956741395</v>
+        <v>0.5404799732419099</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>15.567</v>
+        <v>14.627</v>
       </c>
       <c r="V2">
-        <v>0.1262202834625239</v>
+        <v>0.2152390482216696</v>
       </c>
       <c r="W2">
-        <v>0.05870956581906245</v>
+        <v>0.02853881278538813</v>
       </c>
       <c r="X2">
-        <v>0.04485092821450865</v>
+        <v>0.08441127901971202</v>
       </c>
       <c r="Y2">
-        <v>0.0138586376045538</v>
+        <v>-0.05587246623432389</v>
       </c>
       <c r="Z2">
-        <v>0.1869278098504221</v>
+        <v>0.1502836456440629</v>
       </c>
       <c r="AA2">
-        <v>0.01493737583495156</v>
+        <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05082109034564945</v>
+        <v>0.09404495170720109</v>
       </c>
       <c r="AC2">
-        <v>-0.02463145048113492</v>
+        <v>-0.07315449841150433</v>
       </c>
       <c r="AD2">
-        <v>199.687</v>
+        <v>155.18</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>199.687</v>
+        <v>155.18</v>
       </c>
       <c r="AG2">
-        <v>184.12</v>
+        <v>140.553</v>
       </c>
       <c r="AH2">
-        <v>0.6181896420953567</v>
+        <v>0.695447191635632</v>
       </c>
       <c r="AI2">
-        <v>0.5031496142352485</v>
+        <v>0.5032135885179876</v>
       </c>
       <c r="AJ2">
-        <v>0.5988577078698464</v>
+        <v>0.6740827778044218</v>
       </c>
       <c r="AK2">
-        <v>0.4828655125659901</v>
+        <v>0.4784766690155949</v>
       </c>
       <c r="AL2">
-        <v>7.453</v>
+        <v>10.209</v>
       </c>
       <c r="AM2">
-        <v>6.865</v>
+        <v>9.683999999999999</v>
       </c>
       <c r="AN2">
-        <v>12.94231641713656</v>
+        <v>9.228116079923883</v>
       </c>
       <c r="AO2">
-        <v>1.824231852945123</v>
+        <v>1.572729944166912</v>
       </c>
       <c r="AP2">
-        <v>11.933372221142</v>
+        <v>8.358289724072312</v>
       </c>
       <c r="AQ2">
-        <v>1.980480699198835</v>
+        <v>1.657992565055762</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KASB Modaraba (KASE:KASBM)</t>
+          <t>First Punjab Modaraba (KASE:FPJM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,47 +721,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.436</v>
-      </c>
-      <c r="E3">
-        <v>0.327</v>
-      </c>
       <c r="G3">
-        <v>3.173913043478261</v>
+        <v>0.7738317757009345</v>
       </c>
       <c r="H3">
-        <v>3.173913043478261</v>
+        <v>0.7738317757009345</v>
       </c>
       <c r="I3">
-        <v>3.695652173913044</v>
+        <v>0.7635514018691588</v>
       </c>
       <c r="J3">
-        <v>3.675889328063242</v>
+        <v>0.3817757009345794</v>
       </c>
       <c r="K3">
-        <v>0.187</v>
+        <v>-0.031</v>
       </c>
       <c r="L3">
-        <v>4.065217391304348</v>
+        <v>-0.02897196261682243</v>
       </c>
       <c r="M3">
-        <v>0.1443</v>
+        <v>0.001</v>
       </c>
       <c r="N3">
-        <v>0.2633211678832117</v>
+        <v>0.003846153846153846</v>
       </c>
       <c r="O3">
-        <v>0.7716577540106953</v>
+        <v>-0.03225806451612903</v>
       </c>
       <c r="P3">
-        <v>0.1443</v>
+        <v>0.001</v>
       </c>
       <c r="Q3">
-        <v>0.2633211678832117</v>
+        <v>0.003846153846153846</v>
       </c>
       <c r="R3">
-        <v>0.7716577540106953</v>
+        <v>-0.03225806451612903</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,58 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.802</v>
+        <v>0.391</v>
       </c>
       <c r="V3">
-        <v>1.463503649635036</v>
-      </c>
-      <c r="W3">
-        <v>0.2223543400713436</v>
+        <v>1.503846153846154</v>
       </c>
       <c r="X3">
-        <v>0.04351801465583368</v>
-      </c>
-      <c r="Y3">
-        <v>0.17883632541551</v>
-      </c>
-      <c r="Z3">
-        <v>0.116751269035533</v>
-      </c>
-      <c r="AA3">
-        <v>0.4291647438855561</v>
+        <v>0.7000691065708884</v>
       </c>
       <c r="AB3">
-        <v>0.0490598490706845</v>
-      </c>
-      <c r="AC3">
-        <v>0.3801048948148716</v>
+        <v>0.126096150873695</v>
       </c>
       <c r="AD3">
-        <v>0.301</v>
+        <v>7.77</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.301</v>
+        <v>7.77</v>
       </c>
       <c r="AG3">
-        <v>-0.5010000000000001</v>
+        <v>7.379</v>
       </c>
       <c r="AH3">
-        <v>0.3545347467608952</v>
+        <v>0.9676214196762142</v>
       </c>
       <c r="AI3">
-        <v>0.2557349192863211</v>
+        <v>0.92643376654346</v>
       </c>
       <c r="AJ3">
-        <v>-10.65957446808512</v>
+        <v>0.9659641314308156</v>
       </c>
       <c r="AK3">
-        <v>-1.336000000000001</v>
+        <v>0.9228364182091046</v>
       </c>
       <c r="AL3">
-        <v>0.042</v>
+        <v>0.78</v>
       </c>
       <c r="AM3">
-        <v>-0.001999999999999995</v>
+        <v>0.78</v>
       </c>
       <c r="AN3">
-        <v>1.739884393063584</v>
+        <v>9.418181818181818</v>
       </c>
       <c r="AO3">
-        <v>4.047619047619047</v>
+        <v>1.047435897435897</v>
       </c>
       <c r="AP3">
-        <v>-2.895953757225434</v>
+        <v>8.944242424242423</v>
       </c>
       <c r="AQ3">
-        <v>-85.00000000000023</v>
+        <v>1.047435897435897</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +826,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Saudi Pak Leasing Company Limited (KASE:SPLC)</t>
+          <t>B.R.R. Guardian Modaraba (KASE:BRR)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,115 +835,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.416</v>
+        <v>0.327</v>
+      </c>
+      <c r="E4">
+        <v>0.349</v>
       </c>
       <c r="G4">
-        <v>0.75</v>
+        <v>0.812366737739872</v>
       </c>
       <c r="H4">
-        <v>0.75</v>
+        <v>0.812366737739872</v>
       </c>
       <c r="I4">
-        <v>22.75</v>
+        <v>0.7249466950959488</v>
       </c>
       <c r="J4">
-        <v>22.75</v>
+        <v>0.6360965208799209</v>
       </c>
       <c r="K4">
-        <v>-0.08</v>
+        <v>2.88</v>
       </c>
       <c r="L4">
-        <v>-20</v>
+        <v>0.6140724946695095</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>0.533</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.1055445544554456</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.1850694444444445</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>0.533</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.1055445544554456</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.1850694444444445</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>0.116</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="V4">
-        <v>0.2421711899791232</v>
+        <v>0.001782178217821782</v>
       </c>
       <c r="W4">
-        <v>0.01232665639445301</v>
+        <v>0.1531914893617021</v>
       </c>
       <c r="X4">
-        <v>0.1443381253372817</v>
+        <v>0.07278895963491754</v>
       </c>
       <c r="Y4">
-        <v>-0.1320114689428287</v>
+        <v>0.08040252972678459</v>
       </c>
       <c r="Z4">
-        <v>0.010498687664042</v>
+        <v>0.243042960045603</v>
       </c>
       <c r="AA4">
-        <v>0.2388451443569554</v>
+        <v>0.1545987813093657</v>
       </c>
       <c r="AB4">
-        <v>0.07108619947506162</v>
+        <v>0.07802277446640681</v>
       </c>
       <c r="AC4">
-        <v>0.1677589448818938</v>
+        <v>0.07657600684295886</v>
       </c>
       <c r="AD4">
-        <v>3.59</v>
+        <v>1.01</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.59</v>
+        <v>1.01</v>
       </c>
       <c r="AG4">
-        <v>3.474</v>
+        <v>1.001</v>
       </c>
       <c r="AH4">
-        <v>0.882280658638486</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="AI4">
-        <v>8.547619047619049</v>
+        <v>0.07107670654468684</v>
       </c>
       <c r="AJ4">
-        <v>0.8788262079433341</v>
+        <v>0.1654272021153529</v>
       </c>
       <c r="AK4">
-        <v>11.42763157894737</v>
+        <v>0.07048799380325331</v>
       </c>
       <c r="AL4">
-        <v>0.217</v>
+        <v>0.08</v>
       </c>
       <c r="AM4">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="AN4">
-        <v>30.94827586206896</v>
+        <v>0.2774725274725275</v>
       </c>
       <c r="AO4">
-        <v>0.4193548387096774</v>
+        <v>42.5</v>
       </c>
       <c r="AP4">
-        <v>29.94827586206896</v>
+        <v>0.275</v>
       </c>
       <c r="AQ4">
-        <v>0.4333333333333333</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="5">
@@ -975,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B.R.R. Guardian Modaraba (KASE:BRR)</t>
+          <t>KASB Modaraba (KASE:KASBM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -984,46 +969,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.118</v>
+        <v>-0.123</v>
       </c>
       <c r="E5">
-        <v>0.337</v>
+        <v>0.0992</v>
       </c>
       <c r="G5">
-        <v>0.7142857142857142</v>
+        <v>0.5957446808510639</v>
       </c>
       <c r="H5">
-        <v>0.7142857142857142</v>
+        <v>0.5957446808510639</v>
       </c>
       <c r="I5">
-        <v>0.5505226480836237</v>
+        <v>0.4680851063829788</v>
       </c>
       <c r="J5">
-        <v>0.5484581881533102</v>
+        <v>0.3343465045592706</v>
       </c>
       <c r="K5">
-        <v>1.6</v>
+        <v>0.025</v>
       </c>
       <c r="L5">
-        <v>0.5574912891986062</v>
+        <v>0.1773049645390071</v>
       </c>
       <c r="M5">
-        <v>0.382</v>
+        <v>0.101</v>
       </c>
       <c r="N5">
-        <v>0.05544267053701016</v>
+        <v>0.3519163763066203</v>
       </c>
       <c r="O5">
-        <v>0.23875</v>
+        <v>4.04</v>
       </c>
       <c r="P5">
-        <v>0.382</v>
+        <v>0.101</v>
       </c>
       <c r="Q5">
-        <v>0.05544267053701016</v>
+        <v>0.3519163763066203</v>
       </c>
       <c r="R5">
-        <v>0.23875</v>
+        <v>4.04</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1032,73 +1017,73 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.24</v>
+        <v>0.019</v>
       </c>
       <c r="V5">
-        <v>0.03483309143686502</v>
+        <v>0.06620209059233449</v>
       </c>
       <c r="W5">
-        <v>0.1300813008130081</v>
+        <v>0.02853881278538813</v>
       </c>
       <c r="X5">
-        <v>0.03709759648159173</v>
+        <v>0.08512916064151593</v>
       </c>
       <c r="Y5">
-        <v>0.09298370433141639</v>
+        <v>-0.05659034785612781</v>
       </c>
       <c r="Z5">
-        <v>0.2205995388162952</v>
+        <v>0.3759999999999999</v>
       </c>
       <c r="AA5">
-        <v>0.1209896233666411</v>
+        <v>0.1257142857142857</v>
       </c>
       <c r="AB5">
-        <v>0.03922846140749052</v>
+        <v>0.09469196297750399</v>
       </c>
       <c r="AC5">
-        <v>0.08176116195915054</v>
+        <v>0.03102232273678174</v>
       </c>
       <c r="AD5">
-        <v>0.737</v>
+        <v>0.225</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.737</v>
+        <v>0.225</v>
       </c>
       <c r="AG5">
-        <v>0.497</v>
+        <v>0.206</v>
       </c>
       <c r="AH5">
-        <v>0.09663039202832044</v>
+        <v>0.439453125</v>
       </c>
       <c r="AI5">
-        <v>0.03772329426216922</v>
+        <v>0.2497225305216426</v>
       </c>
       <c r="AJ5">
-        <v>0.06728035738459456</v>
+        <v>0.4178498985801217</v>
       </c>
       <c r="AK5">
-        <v>0.0257552987511012</v>
+        <v>0.2335600907029478</v>
       </c>
       <c r="AL5">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="AM5">
-        <v>0.04</v>
+        <v>0.025</v>
       </c>
       <c r="AN5">
-        <v>0.3798969072164948</v>
+        <v>2.710843373493976</v>
       </c>
       <c r="AO5">
-        <v>39.5</v>
+        <v>2.64</v>
       </c>
       <c r="AP5">
-        <v>0.2561855670103093</v>
+        <v>2.481927710843374</v>
       </c>
       <c r="AQ5">
-        <v>39.5</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="6">
@@ -1118,118 +1103,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0969</v>
+        <v>0.106</v>
       </c>
       <c r="E6">
-        <v>-0.14</v>
+        <v>0.0775</v>
       </c>
       <c r="G6">
-        <v>0.397489539748954</v>
+        <v>0.4483985765124555</v>
       </c>
       <c r="H6">
-        <v>0.397489539748954</v>
+        <v>0.4483985765124555</v>
       </c>
       <c r="I6">
-        <v>0.2803347280334728</v>
+        <v>0.4270462633451957</v>
       </c>
       <c r="J6">
-        <v>0.2658346558938104</v>
+        <v>0.360204239517252</v>
       </c>
       <c r="K6">
-        <v>0.055</v>
+        <v>0.097</v>
       </c>
       <c r="L6">
-        <v>0.2301255230125523</v>
+        <v>0.3451957295373665</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.04518950437317784</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.3195876288659794</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>0.031</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.04518950437317784</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.3195876288659794</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>1.38</v>
+        <v>0.443</v>
       </c>
       <c r="V6">
-        <v>1.516483516483516</v>
+        <v>0.6457725947521865</v>
       </c>
       <c r="W6">
-        <v>0.02165354330708661</v>
+        <v>0.037890625</v>
       </c>
       <c r="X6">
-        <v>0.04021867344637467</v>
+        <v>0.07530872037087352</v>
       </c>
       <c r="Y6">
-        <v>-0.01856513013928806</v>
+        <v>-0.03741809537087352</v>
       </c>
       <c r="Z6">
-        <v>0.2366336633663366</v>
+        <v>0.1907671418873048</v>
       </c>
       <c r="AA6">
-        <v>0.06290542847388188</v>
+        <v>0.06871513326839634</v>
       </c>
       <c r="AB6">
-        <v>0.04482937510535254</v>
+        <v>0.08295100444535147</v>
       </c>
       <c r="AC6">
-        <v>0.01807605336852934</v>
+        <v>-0.01423587117695513</v>
       </c>
       <c r="AD6">
-        <v>0.293</v>
+        <v>0.219</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.293</v>
+        <v>0.219</v>
       </c>
       <c r="AG6">
-        <v>-1.087</v>
+        <v>-0.224</v>
       </c>
       <c r="AH6">
-        <v>0.2435577722360764</v>
+        <v>0.2419889502762431</v>
       </c>
       <c r="AI6">
-        <v>0.1026989134244655</v>
+        <v>0.09869310500225327</v>
       </c>
       <c r="AJ6">
-        <v>6.141242937853109</v>
+        <v>-0.4848484848484848</v>
       </c>
       <c r="AK6">
-        <v>-0.7379497623896809</v>
+        <v>-0.1261261261261261</v>
       </c>
       <c r="AL6">
-        <v>0.006</v>
+        <v>0.025</v>
       </c>
       <c r="AM6">
-        <v>0.006</v>
+        <v>0.025</v>
       </c>
       <c r="AN6">
-        <v>3.329545454545455</v>
+        <v>1.598540145985401</v>
       </c>
       <c r="AO6">
-        <v>11.16666666666667</v>
+        <v>4.8</v>
       </c>
       <c r="AP6">
-        <v>-12.35227272727273</v>
+        <v>-1.635036496350365</v>
       </c>
       <c r="AQ6">
-        <v>11.16666666666667</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="7">
@@ -1240,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Habib Modaraba (KASE:FHAM)</t>
+          <t>Pak-Gulf Leasing Company Limited (KASE:PGLC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1249,46 +1237,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.154</v>
+        <v>0.0764</v>
       </c>
       <c r="E7">
-        <v>0.0316</v>
+        <v>0.272</v>
       </c>
       <c r="G7">
-        <v>0.7925170068027211</v>
+        <v>0.7333333333333332</v>
       </c>
       <c r="H7">
-        <v>0.7925170068027211</v>
+        <v>0.7333333333333332</v>
       </c>
       <c r="I7">
-        <v>0.7925170068027211</v>
+        <v>0.7207207207207207</v>
       </c>
       <c r="J7">
-        <v>0.7343276950419807</v>
+        <v>0.6326526027274156</v>
       </c>
       <c r="K7">
-        <v>2.05</v>
+        <v>0.703</v>
       </c>
       <c r="L7">
-        <v>0.3486394557823129</v>
+        <v>0.6333333333333332</v>
       </c>
       <c r="M7">
-        <v>1.64</v>
+        <v>0.1016</v>
       </c>
       <c r="N7">
-        <v>0.1623762376237624</v>
+        <v>0.1369272237196766</v>
       </c>
       <c r="O7">
-        <v>0.8</v>
+        <v>0.1445234708392603</v>
       </c>
       <c r="P7">
-        <v>1.64</v>
+        <v>0.1016</v>
       </c>
       <c r="Q7">
-        <v>0.1623762376237624</v>
+        <v>0.1369272237196766</v>
       </c>
       <c r="R7">
-        <v>0.8</v>
+        <v>0.1445234708392603</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1297,73 +1285,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>1.45</v>
+        <v>0.129</v>
       </c>
       <c r="V7">
-        <v>0.1435643564356436</v>
+        <v>0.1738544474393531</v>
       </c>
       <c r="W7">
-        <v>0.09808612440191387</v>
+        <v>0.1555309734513274</v>
       </c>
       <c r="X7">
-        <v>0.1046749038947598</v>
+        <v>0.1408995674287781</v>
       </c>
       <c r="Y7">
-        <v>-0.006588779492845906</v>
+        <v>0.01463140602254936</v>
       </c>
       <c r="Z7">
-        <v>0.1110481586402266</v>
+        <v>0.1365313653136532</v>
       </c>
       <c r="AA7">
-        <v>0.08154573837293384</v>
+        <v>0.08637692361961027</v>
       </c>
       <c r="AB7">
-        <v>0.06883756967522087</v>
+        <v>0.1145788222232604</v>
       </c>
       <c r="AC7">
-        <v>0.01270816869771298</v>
+        <v>-0.02820189860365008</v>
       </c>
       <c r="AD7">
-        <v>48.1</v>
+        <v>2.54</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>48.1</v>
+        <v>2.54</v>
       </c>
       <c r="AG7">
-        <v>46.65</v>
+        <v>2.411</v>
       </c>
       <c r="AH7">
-        <v>0.8264604810996563</v>
+        <v>0.7739183424741012</v>
       </c>
       <c r="AI7">
-        <v>0.6736694677871148</v>
+        <v>0.3907692307692308</v>
       </c>
       <c r="AJ7">
-        <v>0.8220264317180617</v>
+        <v>0.7646685696162385</v>
       </c>
       <c r="AK7">
-        <v>0.6669049320943531</v>
+        <v>0.378433526918851</v>
       </c>
       <c r="AL7">
-        <v>2.75</v>
+        <v>0.349</v>
       </c>
       <c r="AM7">
-        <v>2.506</v>
+        <v>0.349</v>
       </c>
       <c r="AN7">
-        <v>10.98173515981735</v>
+        <v>3.17103620474407</v>
       </c>
       <c r="AO7">
-        <v>1.694545454545455</v>
+        <v>2.292263610315187</v>
       </c>
       <c r="AP7">
-        <v>10.65068493150685</v>
+        <v>3.009987515605493</v>
       </c>
       <c r="AQ7">
-        <v>1.859537110933759</v>
+        <v>2.292263610315187</v>
       </c>
     </row>
     <row r="8">
@@ -1374,7 +1362,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ORIX Modaraba (KASE:ORIXM)</t>
+          <t>First Habib Modaraba (KASE:FHAM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1383,46 +1371,46 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.025</v>
+        <v>0.289</v>
       </c>
       <c r="E8">
-        <v>0.00444</v>
+        <v>0.075</v>
       </c>
       <c r="G8">
-        <v>0.2770199370409234</v>
+        <v>0.764018691588785</v>
       </c>
       <c r="H8">
-        <v>0.2770199370409234</v>
+        <v>0.764018691588785</v>
       </c>
       <c r="I8">
-        <v>0.25498426023085</v>
+        <v>0.8691588785046729</v>
       </c>
       <c r="J8">
-        <v>0.2448911332633788</v>
+        <v>0.6754395691430382</v>
       </c>
       <c r="K8">
-        <v>0.922</v>
+        <v>1.83</v>
       </c>
       <c r="L8">
-        <v>0.09674711437565583</v>
+        <v>0.2137850467289719</v>
       </c>
       <c r="M8">
-        <v>0.7718</v>
+        <v>1.22</v>
       </c>
       <c r="N8">
-        <v>0.1873300970873786</v>
+        <v>0.1826347305389222</v>
       </c>
       <c r="O8">
-        <v>0.8370932754880694</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P8">
-        <v>0.7718</v>
+        <v>1.22</v>
       </c>
       <c r="Q8">
-        <v>0.1873300970873786</v>
+        <v>0.1826347305389222</v>
       </c>
       <c r="R8">
-        <v>0.8370932754880694</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1431,73 +1419,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>0.1586826347305389</v>
       </c>
       <c r="W8">
-        <v>0.1405487804878049</v>
+        <v>0.07854077253218884</v>
       </c>
       <c r="X8">
-        <v>0.1313777923916497</v>
+        <v>0.2416004598118835</v>
       </c>
       <c r="Y8">
-        <v>0.009170988096155214</v>
+        <v>-0.1630596872796947</v>
       </c>
       <c r="Z8">
-        <v>0.3244807626830098</v>
+        <v>0.122373123659757</v>
       </c>
       <c r="AA8">
-        <v>0.07946246169560776</v>
+        <v>0.08265564991943398</v>
       </c>
       <c r="AB8">
-        <v>0.07052924049681726</v>
+        <v>0.1215504364820487</v>
       </c>
       <c r="AC8">
-        <v>0.008933221198790503</v>
+        <v>-0.03889478656261476</v>
       </c>
       <c r="AD8">
-        <v>27.2</v>
+        <v>54.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>27.2</v>
+        <v>54.7</v>
       </c>
       <c r="AG8">
-        <v>27.2</v>
+        <v>53.64</v>
       </c>
       <c r="AH8">
-        <v>0.8684546615581098</v>
+        <v>0.8911697621375041</v>
       </c>
       <c r="AI8">
-        <v>0.8002353633421594</v>
+        <v>0.7629009762900977</v>
       </c>
       <c r="AJ8">
-        <v>0.8684546615581098</v>
+        <v>0.8892572944297082</v>
       </c>
       <c r="AK8">
-        <v>0.8002353633421594</v>
+        <v>0.7593431483578709</v>
       </c>
       <c r="AL8">
-        <v>1.72</v>
+        <v>5.51</v>
       </c>
       <c r="AM8">
-        <v>1.72</v>
+        <v>5.253</v>
       </c>
       <c r="AN8">
-        <v>11.10204081632653</v>
+        <v>7.715091678420311</v>
       </c>
       <c r="AO8">
-        <v>1.412790697674419</v>
+        <v>1.3502722323049</v>
       </c>
       <c r="AP8">
-        <v>11.10204081632653</v>
+        <v>7.565585331452751</v>
       </c>
       <c r="AQ8">
-        <v>1.412790697674419</v>
+        <v>1.416333523700742</v>
       </c>
     </row>
     <row r="9">
@@ -1508,7 +1496,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Capital Securities Corporation Limited (KASE:FCSC)</t>
+          <t>First IBL Modaraba (KASE:FIBLM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1517,28 +1505,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.244</v>
-      </c>
-      <c r="E9">
-        <v>-0.0617</v>
+        <v>-0.0185</v>
       </c>
       <c r="G9">
-        <v>0.3926868044515104</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="H9">
-        <v>0.3926868044515104</v>
+        <v>0.3703703703703703</v>
       </c>
       <c r="I9">
-        <v>0.4467408585055644</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="J9">
-        <v>0.309426826207012</v>
+        <v>0.1703703703703704</v>
       </c>
       <c r="K9">
-        <v>0.819</v>
+        <v>-0.004</v>
       </c>
       <c r="L9">
-        <v>0.1302066772655008</v>
+        <v>-0.02962962962962963</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1547,7 +1532,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1556,79 +1541,73 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.789</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>0.2267241379310345</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>0.1193877551020408</v>
+        <v>-0.003508771929824562</v>
       </c>
       <c r="X9">
-        <v>0.1085413414717698</v>
+        <v>0.06867941023918911</v>
       </c>
       <c r="Y9">
-        <v>0.010846413630271</v>
+        <v>-0.07218818216901367</v>
       </c>
       <c r="Z9">
-        <v>0.2332480439055142</v>
+        <v>0.1681195516811956</v>
       </c>
       <c r="AA9">
-        <v>0.07217320194467704</v>
+        <v>0.02864259028642591</v>
       </c>
       <c r="AB9">
-        <v>0.06914643340860245</v>
+        <v>0.06888935770284112</v>
       </c>
       <c r="AC9">
-        <v>0.003026768536074587</v>
+        <v>-0.04024676741641521</v>
       </c>
       <c r="AD9">
-        <v>17.5</v>
+        <v>0.003</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>17.5</v>
+        <v>0.003</v>
       </c>
       <c r="AG9">
-        <v>16.711</v>
+        <v>0.003</v>
       </c>
       <c r="AH9">
-        <v>0.8341277407054337</v>
+        <v>0.005494505494505494</v>
       </c>
       <c r="AI9">
-        <v>0.6503158677071721</v>
+        <v>0.003592814371257485</v>
       </c>
       <c r="AJ9">
-        <v>0.8276459808825715</v>
+        <v>0.005494505494505494</v>
       </c>
       <c r="AK9">
-        <v>0.6397534550744611</v>
+        <v>0.003592814371257485</v>
       </c>
       <c r="AL9">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>1.493</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>6.183745583038869</v>
-      </c>
-      <c r="AO9">
-        <v>1.578651685393258</v>
+        <v>0.06122448979591837</v>
       </c>
       <c r="AP9">
-        <v>5.90494699646643</v>
-      </c>
-      <c r="AQ9">
-        <v>1.8821165438714</v>
+        <v>0.06122448979591837</v>
       </c>
     </row>
     <row r="10">
@@ -1639,7 +1618,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>First IBL Modaraba (KASE:FIBLM)</t>
+          <t>OLP Modaraba (KASE:OLPM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1648,46 +1627,46 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0735</v>
+        <v>-0.0361</v>
       </c>
       <c r="E10">
-        <v>0.584</v>
+        <v>-0.0344</v>
       </c>
       <c r="G10">
-        <v>0.4366197183098592</v>
+        <v>0.3681948424068767</v>
       </c>
       <c r="H10">
-        <v>0.4366197183098592</v>
+        <v>0.3681948424068767</v>
       </c>
       <c r="I10">
-        <v>0.2323943661971831</v>
+        <v>0.3896848137535817</v>
       </c>
       <c r="J10">
-        <v>0.2323943661971831</v>
+        <v>0.2727196935457685</v>
       </c>
       <c r="K10">
-        <v>0.034</v>
+        <v>0.457</v>
       </c>
       <c r="L10">
-        <v>0.2394366197183099</v>
+        <v>0.0654727793696275</v>
       </c>
       <c r="M10">
-        <v>0.016</v>
+        <v>0.57</v>
       </c>
       <c r="N10">
-        <v>0.01754385964912281</v>
+        <v>0.2235294117647059</v>
       </c>
       <c r="O10">
-        <v>0.4705882352941176</v>
+        <v>1.2472647702407</v>
       </c>
       <c r="P10">
-        <v>0.016</v>
+        <v>0.57</v>
       </c>
       <c r="Q10">
-        <v>0.01754385964912281</v>
+        <v>0.2235294117647059</v>
       </c>
       <c r="R10">
-        <v>0.4705882352941176</v>
+        <v>1.2472647702407</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1696,67 +1675,73 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.341</v>
+        <v>3.78</v>
       </c>
       <c r="V10">
-        <v>0.3739035087719298</v>
+        <v>1.482352941176471</v>
       </c>
       <c r="W10">
-        <v>0.02931034482758621</v>
+        <v>0.07359098228663447</v>
       </c>
       <c r="X10">
-        <v>0.03560854934834282</v>
+        <v>0.2384432658752325</v>
       </c>
       <c r="Y10">
-        <v>-0.006298204520756606</v>
+        <v>-0.164852283588598</v>
       </c>
       <c r="Z10">
-        <v>0.15203426124197</v>
+        <v>0.2441413081497027</v>
       </c>
       <c r="AA10">
-        <v>0.03533190578158459</v>
+        <v>0.06658214274044996</v>
       </c>
       <c r="AB10">
-        <v>0.03571134739380646</v>
+        <v>0.1214434804672813</v>
       </c>
       <c r="AC10">
-        <v>-0.0003794416122218716</v>
+        <v>-0.05486133772683133</v>
       </c>
       <c r="AD10">
-        <v>0.004</v>
+        <v>20.5</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0.004</v>
+        <v>20.5</v>
       </c>
       <c r="AG10">
-        <v>-0.337</v>
+        <v>16.72</v>
       </c>
       <c r="AH10">
-        <v>0.004366812227074236</v>
+        <v>0.8893709327548807</v>
       </c>
       <c r="AI10">
-        <v>0.003496503496503497</v>
+        <v>0.8134920634920635</v>
       </c>
       <c r="AJ10">
-        <v>-0.5860869565217393</v>
+        <v>0.8676699532952776</v>
       </c>
       <c r="AK10">
-        <v>-0.4196762141967622</v>
+        <v>0.7805788982259571</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AN10">
-        <v>0.05882352941176471</v>
+        <v>7.454545454545454</v>
+      </c>
+      <c r="AO10">
+        <v>1.301435406698565</v>
       </c>
       <c r="AP10">
-        <v>-4.955882352941177</v>
+        <v>6.079999999999999</v>
+      </c>
+      <c r="AQ10">
+        <v>1.301435406698565</v>
       </c>
     </row>
     <row r="11">
@@ -1767,7 +1752,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UDL Modaraba Management (Private) Limited (KASE:FUDLM)</t>
+          <t>Pakistan Stock Exchange Limited (KASE:PSX)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1776,46 +1761,46 @@
         </is>
       </c>
       <c r="D11">
-        <v>-0.226</v>
+        <v>0.052</v>
       </c>
       <c r="E11">
-        <v>-0.0583</v>
+        <v>-0.0147</v>
       </c>
       <c r="G11">
-        <v>0.277027027027027</v>
+        <v>0.189297124600639</v>
       </c>
       <c r="H11">
-        <v>0.277027027027027</v>
+        <v>0.1661341853035144</v>
       </c>
       <c r="I11">
-        <v>0.1722972972972973</v>
+        <v>0.0009584664536741214</v>
       </c>
       <c r="J11">
-        <v>0.1681949806949807</v>
+        <v>0.0008196755321355961</v>
       </c>
       <c r="K11">
-        <v>0.163</v>
+        <v>1.32</v>
       </c>
       <c r="L11">
-        <v>0.5506756756756758</v>
+        <v>0.2108626198083067</v>
       </c>
       <c r="M11">
-        <v>0.2106</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="N11">
-        <v>0.1504285714285714</v>
+        <v>0.02398601398601399</v>
       </c>
       <c r="O11">
-        <v>1.292024539877301</v>
+        <v>0.5196969696969698</v>
       </c>
       <c r="P11">
-        <v>0.2106</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="Q11">
-        <v>0.1504285714285714</v>
+        <v>0.02398601398601399</v>
       </c>
       <c r="R11">
-        <v>1.292024539877301</v>
+        <v>0.5196969696969698</v>
       </c>
       <c r="S11">
         <v>0</v>
@@ -1824,31 +1809,31 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>0.802</v>
+        <v>1.71</v>
       </c>
       <c r="V11">
-        <v>0.572857142857143</v>
+        <v>0.05979020979020978</v>
       </c>
       <c r="W11">
-        <v>0.04984709480122324</v>
+        <v>0.0227979274611399</v>
       </c>
       <c r="X11">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="Y11">
-        <v>0.01430221153673038</v>
+        <v>-0.04576473421567055</v>
       </c>
       <c r="Z11">
-        <v>0.1104889884285181</v>
+        <v>0.11254944264653</v>
       </c>
       <c r="AA11">
-        <v>0.01858369327574255</v>
+        <v>9.225402429285924e-05</v>
       </c>
       <c r="AB11">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AC11">
-        <v>-0.01696118998875032</v>
+        <v>-0.06847040765251759</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1860,7 +1845,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-0.802</v>
+        <v>-1.71</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1869,22 +1854,25 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-1.34113712374582</v>
+        <v>-0.06359241353663071</v>
       </c>
       <c r="AK11">
-        <v>-0.3017306245297216</v>
+        <v>-0.03959249826348692</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="AN11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>-10.025</v>
+        <v>-2.326530612244898</v>
+      </c>
+      <c r="AQ11">
+        <v>-3</v>
       </c>
     </row>
     <row r="12">
@@ -1895,7 +1883,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>First Punjab Modaraba (KASE:FPJM)</t>
+          <t>Habib Metro Modaraba (KASE:HMM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1903,119 +1891,104 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D12">
-        <v>0.0504</v>
-      </c>
-      <c r="E12">
-        <v>-0.0426</v>
-      </c>
       <c r="G12">
-        <v>0.6598130841121495</v>
+        <v>0</v>
       </c>
       <c r="H12">
-        <v>0.6598130841121495</v>
+        <v>0</v>
       </c>
       <c r="I12">
-        <v>0.6289719626168224</v>
+        <v>0</v>
       </c>
       <c r="J12">
-        <v>0.5154075804776739</v>
+        <v>0</v>
       </c>
       <c r="K12">
-        <v>0.118</v>
+        <v>0.105</v>
       </c>
       <c r="L12">
-        <v>0.1102803738317757</v>
+        <v>0.4838709677419354</v>
       </c>
       <c r="M12">
-        <v>-0</v>
+        <v>0.052</v>
       </c>
       <c r="N12">
-        <v>-0</v>
+        <v>0.0761346998535871</v>
       </c>
       <c r="O12">
-        <v>-0</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="P12">
-        <v>-0</v>
+        <v>0.052</v>
       </c>
       <c r="Q12">
-        <v>-0</v>
+        <v>0.0761346998535871</v>
       </c>
       <c r="R12">
-        <v>-0</v>
+        <v>0.4952380952380953</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
       <c r="U12">
-        <v>0.575</v>
+        <v>0.612</v>
       </c>
       <c r="V12">
-        <v>1.280623608017817</v>
+        <v>0.8960468521229867</v>
       </c>
       <c r="W12">
-        <v>0.1484276729559748</v>
+        <v>0.05440414507772021</v>
       </c>
       <c r="X12">
-        <v>0.3016152315482593</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="Y12">
-        <v>-0.1531875585922845</v>
+        <v>-0.01415851659909025</v>
       </c>
       <c r="Z12">
-        <v>0.1043495221377024</v>
+        <v>0.1202882483370288</v>
       </c>
       <c r="AA12">
-        <v>0.05378253472899465</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.07169305132457472</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AC12">
-        <v>-0.01791051659558007</v>
+        <v>-0.06856266167681045</v>
       </c>
       <c r="AD12">
-        <v>8.23</v>
+        <v>0</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>8.23</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>7.655</v>
+        <v>-0.612</v>
       </c>
       <c r="AH12">
-        <v>0.9482659292545225</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>0.9017201709214419</v>
+        <v>0</v>
       </c>
       <c r="AJ12">
-        <v>0.9445952615992101</v>
+        <v>-8.619718309859147</v>
       </c>
       <c r="AK12">
-        <v>0.8951122544434051</v>
+        <v>-0.7391304347826088</v>
       </c>
       <c r="AL12">
-        <v>0.678</v>
+        <v>0</v>
       </c>
       <c r="AM12">
-        <v>0.678</v>
-      </c>
-      <c r="AN12">
-        <v>12.03216374269006</v>
-      </c>
-      <c r="AO12">
-        <v>0.9926253687315634</v>
-      </c>
-      <c r="AP12">
-        <v>11.19152046783626</v>
-      </c>
-      <c r="AQ12">
-        <v>0.9926253687315634</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -2026,7 +1999,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>First Elite Capital Modaraba (KASE:FECM)</t>
+          <t>First Fidelity Leasing Modaraba (KASE:FFLM)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2035,76 +2008,73 @@
         </is>
       </c>
       <c r="D13">
-        <v>-0.00334</v>
+        <v>0.541</v>
       </c>
       <c r="G13">
-        <v>0.1212121212121212</v>
+        <v>-0.08888888888888889</v>
       </c>
       <c r="H13">
-        <v>0.1212121212121212</v>
+        <v>-0.08888888888888889</v>
       </c>
       <c r="I13">
-        <v>0.04166666666666666</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="J13">
-        <v>0.0234375</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="K13">
-        <v>0.008999999999999999</v>
+        <v>-0.027</v>
       </c>
       <c r="L13">
-        <v>0.03409090909090909</v>
+        <v>-0.3</v>
       </c>
       <c r="M13">
-        <v>0.0226</v>
+        <v>-0</v>
       </c>
       <c r="N13">
-        <v>0.09300411522633746</v>
+        <v>-0</v>
       </c>
       <c r="O13">
-        <v>2.511111111111112</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>0.0226</v>
+        <v>-0</v>
       </c>
       <c r="Q13">
-        <v>0.09300411522633746</v>
+        <v>-0</v>
       </c>
       <c r="R13">
-        <v>2.511111111111112</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
       <c r="U13">
-        <v>0.142</v>
+        <v>0</v>
       </c>
       <c r="V13">
-        <v>0.5843621399176955</v>
+        <v>0</v>
       </c>
       <c r="W13">
-        <v>0.01361573373676248</v>
+        <v>-0.01377551020408163</v>
       </c>
       <c r="X13">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="Y13">
-        <v>-0.02192914952773039</v>
+        <v>-0.08233817188089208</v>
       </c>
       <c r="Z13">
-        <v>0.4817518248175182</v>
+        <v>0.04591836734693878</v>
       </c>
       <c r="AA13">
-        <v>0.01129105839416058</v>
+        <v>-0.004591836734693877</v>
       </c>
       <c r="AB13">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AC13">
-        <v>-0.02425382487033228</v>
+        <v>-0.07315449841150433</v>
       </c>
       <c r="AD13">
         <v>0</v>
@@ -2116,7 +2086,7 @@
         <v>0</v>
       </c>
       <c r="AG13">
-        <v>-0.142</v>
+        <v>0</v>
       </c>
       <c r="AH13">
         <v>0</v>
@@ -2125,10 +2095,10 @@
         <v>0</v>
       </c>
       <c r="AJ13">
-        <v>-1.405940594059406</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>-0.2939958592132505</v>
+        <v>0</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2137,10 +2107,10 @@
         <v>0</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP13">
-        <v>-10.14285714285714</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2151,7 +2121,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pakistan Stock Exchange Limited (KASE:PSX)</t>
+          <t>UDL Modaraba Management (Private) Limited (KASE:FUDLM)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2160,46 +2130,46 @@
         </is>
       </c>
       <c r="D14">
-        <v>0.0623</v>
+        <v>-0.249</v>
       </c>
       <c r="E14">
-        <v>0.454</v>
+        <v>0.225</v>
       </c>
       <c r="G14">
-        <v>0.2648044692737431</v>
+        <v>-0.009569377990430623</v>
       </c>
       <c r="H14">
-        <v>0.2435754189944135</v>
+        <v>-0.009569377990430623</v>
       </c>
       <c r="I14">
-        <v>0.06446927374301677</v>
+        <v>-0.1196172248803828</v>
       </c>
       <c r="J14">
-        <v>0.06206120157956602</v>
+        <v>-0.1126588821588093</v>
       </c>
       <c r="K14">
-        <v>4.07</v>
+        <v>0.34</v>
       </c>
       <c r="L14">
-        <v>0.4547486033519554</v>
+        <v>1.626794258373206</v>
       </c>
       <c r="M14">
-        <v>0.8015</v>
+        <v>0.323</v>
       </c>
       <c r="N14">
-        <v>0.012824</v>
+        <v>0.3336776859504132</v>
       </c>
       <c r="O14">
-        <v>0.1969287469287469</v>
+        <v>0.95</v>
       </c>
       <c r="P14">
-        <v>0.8015</v>
+        <v>0.323</v>
       </c>
       <c r="Q14">
-        <v>0.012824</v>
+        <v>0.3336776859504132</v>
       </c>
       <c r="R14">
-        <v>0.1969287469287469</v>
+        <v>0.95</v>
       </c>
       <c r="S14">
         <v>0</v>
@@ -2208,31 +2178,31 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2.28</v>
+        <v>0.303</v>
       </c>
       <c r="V14">
-        <v>0.03648</v>
+        <v>0.3130165289256198</v>
       </c>
       <c r="W14">
-        <v>0.07333333333333333</v>
+        <v>0.08740359897172237</v>
       </c>
       <c r="X14">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="Y14">
-        <v>0.03778845006884047</v>
+        <v>0.01884093729491192</v>
       </c>
       <c r="Z14">
-        <v>0.1697647951441578</v>
+        <v>0.06541471048513302</v>
       </c>
       <c r="AA14">
-        <v>0.01053580717255531</v>
+        <v>-0.007369548159997225</v>
       </c>
       <c r="AB14">
-        <v>0.03554488326449286</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AC14">
-        <v>-0.02500907609193756</v>
+        <v>-0.07593220983680768</v>
       </c>
       <c r="AD14">
         <v>0</v>
@@ -2244,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="AG14">
-        <v>-2.28</v>
+        <v>-0.303</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -2253,25 +2223,22 @@
         <v>0</v>
       </c>
       <c r="AJ14">
-        <v>-0.03786117568913982</v>
+        <v>-0.4556390977443608</v>
       </c>
       <c r="AK14">
-        <v>-0.04099244875943905</v>
+        <v>-0.1431270666036845</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>-0.006</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AP14">
-        <v>-1.080568720379147</v>
-      </c>
-      <c r="AQ14">
-        <v>-96.16666666666666</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="15">
@@ -2282,7 +2249,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pak-Gulf Leasing Company Limited (KASE:PGLC)</t>
+          <t>Next Capital Limited (KASE:NEXT)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2291,121 +2258,106 @@
         </is>
       </c>
       <c r="D15">
-        <v>0.0106</v>
+        <v>-0.0202</v>
       </c>
       <c r="E15">
-        <v>-0.352</v>
+        <v>-0.125</v>
       </c>
       <c r="G15">
-        <v>0.9806034482758621</v>
+        <v>0</v>
       </c>
       <c r="H15">
-        <v>0.9806034482758621</v>
+        <v>0</v>
       </c>
       <c r="I15">
-        <v>0.668103448275862</v>
+        <v>0</v>
       </c>
       <c r="J15">
-        <v>0.334051724137931</v>
+        <v>0</v>
       </c>
       <c r="K15">
-        <v>0.026</v>
+        <v>0.133</v>
       </c>
       <c r="L15">
-        <v>0.02801724137931034</v>
+        <v>0.09300699300699301</v>
       </c>
       <c r="M15">
-        <v>0.037</v>
+        <v>-0</v>
       </c>
       <c r="N15">
-        <v>0.03957219251336898</v>
+        <v>-0</v>
       </c>
       <c r="O15">
-        <v>1.423076923076923</v>
+        <v>-0</v>
       </c>
       <c r="P15">
-        <v>0.037</v>
+        <v>-0</v>
       </c>
       <c r="Q15">
-        <v>0.03957219251336898</v>
+        <v>-0</v>
       </c>
       <c r="R15">
-        <v>1.423076923076923</v>
+        <v>-0</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
       <c r="U15">
-        <v>0.13</v>
+        <v>1.17</v>
       </c>
       <c r="V15">
-        <v>0.1390374331550802</v>
+        <v>0.9590163934426229</v>
       </c>
       <c r="W15">
-        <v>0.005579399141630901</v>
+        <v>0.04836363636363637</v>
       </c>
       <c r="X15">
-        <v>0.09360835173565259</v>
+        <v>0.08226348825411661</v>
       </c>
       <c r="Y15">
-        <v>-0.08802895259402169</v>
+        <v>-0.03389985189048025</v>
       </c>
       <c r="Z15">
-        <v>0.1259500542888165</v>
+        <v>0.6559633027522936</v>
       </c>
       <c r="AA15">
-        <v>0.04207383279044517</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.06777164998556345</v>
+        <v>0.09088871602759331</v>
       </c>
       <c r="AC15">
-        <v>-0.02569781719511829</v>
+        <v>-0.09088871602759331</v>
       </c>
       <c r="AD15">
-        <v>3.74</v>
+        <v>0.791</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>3.74</v>
+        <v>0.791</v>
       </c>
       <c r="AG15">
-        <v>3.61</v>
+        <v>-0.3789999999999999</v>
       </c>
       <c r="AH15">
-        <v>0.7999999999999999</v>
+        <v>0.3933366484336151</v>
       </c>
       <c r="AI15">
-        <v>0.4527845036319613</v>
+        <v>0.2653471989265347</v>
       </c>
       <c r="AJ15">
-        <v>0.7942794279427944</v>
+        <v>-0.4506539833531508</v>
       </c>
       <c r="AK15">
-        <v>0.4440344403444035</v>
+        <v>-0.2092766427388183</v>
       </c>
       <c r="AL15">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>0.22</v>
-      </c>
-      <c r="AN15">
-        <v>5.899053627760253</v>
-      </c>
-      <c r="AO15">
-        <v>2.818181818181818</v>
-      </c>
-      <c r="AP15">
-        <v>5.694006309148265</v>
-      </c>
-      <c r="AQ15">
-        <v>2.818181818181818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -2416,7 +2368,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Habib Metro Modaraba (KASE:HMM)</t>
+          <t>Grays Leasing Limited (KASE:GRYL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2424,6 +2376,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D16">
+        <v>0.122</v>
+      </c>
       <c r="G16">
         <v>0</v>
       </c>
@@ -2437,85 +2392,82 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0.08799999999999999</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L16">
-        <v>0.3946188340807175</v>
+        <v>-0.09999999999999999</v>
       </c>
       <c r="M16">
-        <v>0.123</v>
+        <v>-0</v>
       </c>
       <c r="N16">
-        <v>0.07151162790697674</v>
+        <v>-0</v>
       </c>
       <c r="O16">
-        <v>1.397727272727273</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>0.123</v>
+        <v>-0</v>
       </c>
       <c r="Q16">
-        <v>0.07151162790697674</v>
+        <v>-0</v>
       </c>
       <c r="R16">
-        <v>1.397727272727273</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
       <c r="U16">
-        <v>0.126</v>
+        <v>0.13</v>
       </c>
       <c r="V16">
-        <v>0.07325581395348837</v>
+        <v>0.4452054794520549</v>
       </c>
       <c r="W16">
-        <v>0.04631578947368421</v>
+        <v>-0.02432432432432432</v>
       </c>
       <c r="X16">
-        <v>0.03554488326449286</v>
+        <v>0.08441127901971202</v>
       </c>
       <c r="Y16">
-        <v>0.01077090620919135</v>
+        <v>-0.1087356033440363</v>
       </c>
       <c r="Z16">
-        <v>0.1310993533215755</v>
+        <v>0.1339285714285714</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.03554488326449286</v>
+        <v>0.09404495170720109</v>
       </c>
       <c r="AC16">
-        <v>-0.03554488326449286</v>
+        <v>-0.09404495170720109</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>0.219</v>
       </c>
       <c r="AG16">
-        <v>-0.126</v>
+        <v>0.089</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>0.4285714285714285</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>0.4496919917864476</v>
       </c>
       <c r="AJ16">
-        <v>-0.07904642409033878</v>
+        <v>0.2335958005249344</v>
       </c>
       <c r="AK16">
-        <v>-0.06984478935698449</v>
+        <v>0.2492997198879552</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2532,7 +2484,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Next Capital Limited (KASE:NEXT)</t>
+          <t>Trust Modaraba (KASE:TRSM)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2541,25 +2493,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>0.16</v>
+        <v>-0.178</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>-1.129032258064516</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>-1.129032258064516</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>-0.2661290322580646</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>-0.2661290322580646</v>
       </c>
       <c r="K17">
-        <v>0.234</v>
+        <v>-0.005</v>
       </c>
       <c r="L17">
-        <v>0.1251336898395722</v>
+        <v>-0.04032258064516129</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2568,7 +2520,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2577,67 +2529,73 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>2.2</v>
+        <v>0.058</v>
       </c>
       <c r="V17">
-        <v>0.7260726072607262</v>
+        <v>0.3036649214659686</v>
       </c>
       <c r="W17">
-        <v>0.09</v>
+        <v>-0.002604166666666667</v>
       </c>
       <c r="X17">
-        <v>0.04335374907373299</v>
+        <v>0.07210301598726665</v>
       </c>
       <c r="Y17">
-        <v>0.04664625092626701</v>
+        <v>-0.07470718265393332</v>
       </c>
       <c r="Z17">
-        <v>0.8095238095238095</v>
+        <v>0.06663084363245567</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>-0.01773240193444385</v>
       </c>
       <c r="AB17">
-        <v>0.04887880291017636</v>
+        <v>0.07709484847323424</v>
       </c>
       <c r="AC17">
-        <v>-0.04887880291017636</v>
+        <v>-0.09482725040767809</v>
       </c>
       <c r="AD17">
-        <v>1.63</v>
+        <v>0.032</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>1.63</v>
+        <v>0.032</v>
       </c>
       <c r="AG17">
-        <v>-0.5700000000000003</v>
+        <v>-0.026</v>
       </c>
       <c r="AH17">
-        <v>0.3497854077253219</v>
+        <v>0.1434977578475336</v>
       </c>
       <c r="AI17">
-        <v>0.3721461187214612</v>
+        <v>0.02219140083217753</v>
       </c>
       <c r="AJ17">
-        <v>-0.2317073170731709</v>
+        <v>-0.1575757575757576</v>
       </c>
       <c r="AK17">
-        <v>-0.261467889908257</v>
+        <v>-0.01878612716763006</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>-1.066666666666667</v>
+      </c>
+      <c r="AP17">
+        <v>0.8666666666666668</v>
       </c>
     </row>
     <row r="18">
@@ -2648,7 +2606,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grays Leasing Limited (KASE:GRYL)</t>
+          <t>First Capital Securities Corporation Limited (KASE:FCSC)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2657,25 +2615,28 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.113</v>
+        <v>0.12</v>
+      </c>
+      <c r="E18">
+        <v>0.8120000000000001</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>0.3193069306930693</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>0.3193069306930693</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>0.1881188118811881</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>0.1245091458298372</v>
       </c>
       <c r="K18">
-        <v>-0.008</v>
+        <v>0.515</v>
       </c>
       <c r="L18">
-        <v>-0.07079646017699115</v>
+        <v>0.1274752475247525</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2684,7 +2645,7 @@
         <v>-0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2693,67 +2654,79 @@
         <v>-0</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0.052</v>
+        <v>0</v>
       </c>
       <c r="V18">
-        <v>0.1076604554865424</v>
+        <v>0</v>
       </c>
       <c r="W18">
-        <v>-0.02056555269922879</v>
+        <v>0.06830238726790451</v>
       </c>
       <c r="X18">
-        <v>0.04618384177318362</v>
+        <v>0.2139115332519218</v>
       </c>
       <c r="Y18">
-        <v>-0.0667493944724124</v>
+        <v>-0.1456091459840173</v>
       </c>
       <c r="Z18">
-        <v>0.1550068587105624</v>
+        <v>0.1665910684095502</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>0.02074211163055307</v>
       </c>
       <c r="AB18">
-        <v>0.0525823316206144</v>
+        <v>0.1181186588284905</v>
       </c>
       <c r="AC18">
-        <v>-0.0525823316206144</v>
+        <v>-0.09737654719793747</v>
       </c>
       <c r="AD18">
-        <v>0.354</v>
+        <v>13</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>0.354</v>
+        <v>13</v>
       </c>
       <c r="AG18">
-        <v>0.302</v>
+        <v>13</v>
       </c>
       <c r="AH18">
-        <v>0.4229390681003584</v>
+        <v>0.873069173942243</v>
       </c>
       <c r="AI18">
-        <v>0.4889502762430939</v>
+        <v>0.6103286384976525</v>
       </c>
       <c r="AJ18">
-        <v>0.3847133757961784</v>
+        <v>0.873069173942243</v>
       </c>
       <c r="AK18">
-        <v>0.4494047619047619</v>
+        <v>0.6103286384976525</v>
       </c>
       <c r="AL18">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AM18">
-        <v>0</v>
+        <v>1.084</v>
+      </c>
+      <c r="AN18">
+        <v>16.62404092071611</v>
+      </c>
+      <c r="AO18">
+        <v>0.5629629629629629</v>
+      </c>
+      <c r="AP18">
+        <v>16.62404092071611</v>
+      </c>
+      <c r="AQ18">
+        <v>0.7011070110701106</v>
       </c>
     </row>
     <row r="19">
@@ -2764,7 +2737,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First Fidelity Leasing Modaraba (KASE:FFLM)</t>
+          <t>First Dawood Investment Bank Limited (KASE:FDIBL)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2773,25 +2746,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.312</v>
+        <v>0.126</v>
       </c>
       <c r="G19">
-        <v>-0.2352941176470588</v>
+        <v>0</v>
       </c>
       <c r="H19">
-        <v>-0.2352941176470588</v>
+        <v>0</v>
       </c>
       <c r="I19">
-        <v>-0.3025210084033613</v>
+        <v>0</v>
       </c>
       <c r="J19">
-        <v>-0.3025210084033613</v>
+        <v>0</v>
       </c>
       <c r="K19">
-        <v>-0.029</v>
+        <v>-0.171</v>
       </c>
       <c r="L19">
-        <v>-0.2436974789915967</v>
+        <v>-0.5606557377049181</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2815,55 +2788,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>0.013</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>0.01101694915254237</v>
       </c>
       <c r="W19">
-        <v>-0.0145</v>
+        <v>-0.05044247787610619</v>
       </c>
       <c r="X19">
-        <v>0.03554488326449286</v>
+        <v>0.09381300117228075</v>
       </c>
       <c r="Y19">
-        <v>-0.05004488326449286</v>
+        <v>-0.144255479048387</v>
       </c>
       <c r="Z19">
-        <v>0.05973895582329317</v>
+        <v>0.05638750231096321</v>
       </c>
       <c r="AA19">
-        <v>-0.01807228915662651</v>
+        <v>0</v>
       </c>
       <c r="AB19">
-        <v>0.03554488326449286</v>
+        <v>0.09946326175402483</v>
       </c>
       <c r="AC19">
-        <v>-0.05361717242111937</v>
+        <v>-0.09946326175402483</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.397</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>0.5444015444015444</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>0.3700787401574803</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>0.5421032207993791</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>0.3679220437187253</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2880,7 +2853,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>First Dawood Investment Bank Limited (KASE:FDIBL)</t>
+          <t>OLP Financial Services Pakistan Limited (KASE:OLPL)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2888,8 +2861,11 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D20">
+        <v>-0.013</v>
+      </c>
       <c r="E20">
-        <v>-0.32</v>
+        <v>0.027</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2904,82 +2880,85 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0.385</v>
+        <v>3.97</v>
       </c>
       <c r="L20">
-        <v>0.6626506024096386</v>
+        <v>0.2294797687861272</v>
       </c>
       <c r="M20">
-        <v>-0</v>
+        <v>2.81</v>
       </c>
       <c r="N20">
-        <v>-0</v>
+        <v>0.1860927152317881</v>
       </c>
       <c r="O20">
-        <v>-0</v>
+        <v>0.707808564231738</v>
       </c>
       <c r="P20">
-        <v>-0</v>
+        <v>2.81</v>
       </c>
       <c r="Q20">
-        <v>-0</v>
+        <v>0.1860927152317881</v>
       </c>
       <c r="R20">
-        <v>-0</v>
+        <v>0.707808564231738</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
       <c r="U20">
-        <v>0.021</v>
+        <v>4.22</v>
       </c>
       <c r="V20">
-        <v>0.0125</v>
+        <v>0.2794701986754967</v>
       </c>
       <c r="W20">
-        <v>0.1327586206896552</v>
+        <v>0.07738791423001951</v>
       </c>
       <c r="X20">
-        <v>0.05334410127797337</v>
+        <v>0.1402138058672352</v>
       </c>
       <c r="Y20">
-        <v>0.07941451941168182</v>
+        <v>-0.06282589163721569</v>
       </c>
       <c r="Z20">
-        <v>0.114437660035454</v>
+        <v>0.1318999695028972</v>
       </c>
       <c r="AA20">
         <v>0</v>
       </c>
       <c r="AB20">
-        <v>0.05654161812074812</v>
+        <v>0.1081740681468557</v>
       </c>
       <c r="AC20">
-        <v>-0.05654161812074812</v>
+        <v>-0.1081740681468557</v>
       </c>
       <c r="AD20">
-        <v>2.06</v>
+        <v>51.2</v>
       </c>
       <c r="AE20">
         <v>0</v>
       </c>
       <c r="AF20">
-        <v>2.06</v>
+        <v>51.2</v>
       </c>
       <c r="AG20">
-        <v>2.039</v>
+        <v>46.98</v>
       </c>
       <c r="AH20">
-        <v>0.5508021390374331</v>
+        <v>0.7722473604826546</v>
       </c>
       <c r="AI20">
-        <v>0.3779816513761468</v>
+        <v>0.5372507869884575</v>
       </c>
       <c r="AJ20">
-        <v>0.548265662812584</v>
+        <v>0.7567654639175257</v>
       </c>
       <c r="AK20">
-        <v>0.3755756124516486</v>
+        <v>0.5158102766798419</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3005,10 +2984,10 @@
         </is>
       </c>
       <c r="D21">
-        <v>0.08160000000000001</v>
+        <v>0.00176</v>
       </c>
       <c r="E21">
-        <v>0.00643</v>
+        <v>-0.05230000000000001</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -3023,28 +3002,28 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>0.079</v>
+        <v>0.023</v>
       </c>
       <c r="L21">
-        <v>0.06320000000000001</v>
+        <v>0.02486486486486486</v>
       </c>
       <c r="M21">
-        <v>0.04140000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="N21">
-        <v>0.06160714285714286</v>
+        <v>0.05801104972375691</v>
       </c>
       <c r="O21">
-        <v>0.5240506329113925</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="P21">
-        <v>0.04140000000000001</v>
+        <v>0.021</v>
       </c>
       <c r="Q21">
-        <v>0.06160714285714286</v>
+        <v>0.05801104972375691</v>
       </c>
       <c r="R21">
-        <v>0.5240506329113925</v>
+        <v>0.9130434782608696</v>
       </c>
       <c r="S21">
         <v>0</v>
@@ -3053,55 +3032,55 @@
         <v>0</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>0.414</v>
       </c>
       <c r="V21">
-        <v>0</v>
+        <v>1.143646408839779</v>
       </c>
       <c r="W21">
-        <v>0.06422764227642276</v>
+        <v>0.01854838709677419</v>
       </c>
       <c r="X21">
-        <v>0.05800991570869157</v>
+        <v>0.1145032209728087</v>
       </c>
       <c r="Y21">
-        <v>0.006217726567731195</v>
+        <v>-0.09595483387603454</v>
       </c>
       <c r="Z21">
-        <v>0.7110352673492605</v>
+        <v>0.4357041921808761</v>
       </c>
       <c r="AA21">
         <v>0</v>
       </c>
       <c r="AB21">
-        <v>0.06001614304100675</v>
+        <v>0.1092884916093379</v>
       </c>
       <c r="AC21">
-        <v>-0.06001614304100675</v>
+        <v>-0.1092884916093379</v>
       </c>
       <c r="AD21">
-        <v>1.04</v>
+        <v>0.787</v>
       </c>
       <c r="AE21">
         <v>0</v>
       </c>
       <c r="AF21">
-        <v>1.04</v>
+        <v>0.787</v>
       </c>
       <c r="AG21">
-        <v>1.04</v>
+        <v>0.3730000000000001</v>
       </c>
       <c r="AH21">
-        <v>0.6074766355140186</v>
+        <v>0.6849434290687555</v>
       </c>
       <c r="AI21">
-        <v>0.456140350877193</v>
+        <v>0.4538638985005767</v>
       </c>
       <c r="AJ21">
-        <v>0.6074766355140186</v>
+        <v>0.507482993197279</v>
       </c>
       <c r="AK21">
-        <v>0.456140350877193</v>
+        <v>0.2825757575757576</v>
       </c>
       <c r="AL21">
         <v>0</v>
@@ -3126,23 +3105,26 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D22">
+        <v>-0.0515</v>
+      </c>
       <c r="G22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J22">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22">
-        <v>-0.237</v>
+        <v>-0.161</v>
       </c>
       <c r="L22">
-        <v>11.28571428571428</v>
+        <v>-2.515625</v>
       </c>
       <c r="M22">
         <v>-0</v>
@@ -3166,55 +3148,55 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0.002</v>
+        <v>0.008</v>
       </c>
       <c r="V22">
-        <v>0.004056795131845842</v>
+        <v>0.02826855123674912</v>
       </c>
       <c r="W22">
-        <v>-0.9045801526717556</v>
+        <v>-0.9640718562874251</v>
       </c>
       <c r="X22">
-        <v>0.06227998943681184</v>
+        <v>0.1263569129060487</v>
       </c>
       <c r="Y22">
-        <v>-0.9668601421085674</v>
+        <v>-1.090428769193474</v>
       </c>
       <c r="Z22">
-        <v>-0.01788756388415673</v>
+        <v>0.0557006092254134</v>
       </c>
       <c r="AA22">
         <v>0</v>
       </c>
       <c r="AB22">
-        <v>0.06165293481939302</v>
+        <v>0.1121019386823786</v>
       </c>
       <c r="AC22">
-        <v>-0.06165293481939302</v>
+        <v>-0.1121019386823786</v>
       </c>
       <c r="AD22">
-        <v>0.908</v>
+        <v>0.774</v>
       </c>
       <c r="AE22">
         <v>0</v>
       </c>
       <c r="AF22">
-        <v>0.908</v>
+        <v>0.774</v>
       </c>
       <c r="AG22">
-        <v>0.906</v>
+        <v>0.766</v>
       </c>
       <c r="AH22">
-        <v>0.648108493932905</v>
+        <v>0.7322611163670767</v>
       </c>
       <c r="AI22">
-        <v>0.9795037756202805</v>
+        <v>1.025165562913907</v>
       </c>
       <c r="AJ22">
-        <v>0.6476054324517513</v>
+        <v>0.7302192564346998</v>
       </c>
       <c r="AK22">
-        <v>0.9794594594594594</v>
+        <v>1.025435073627845</v>
       </c>
       <c r="AL22">
         <v>0</v>
@@ -3231,7 +3213,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORIX Leasing Pakistan Limited (KASE:OLPL)</t>
+          <t>First Elite Capital Modaraba (KASE:FECM)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3240,46 +3222,43 @@
         </is>
       </c>
       <c r="D23">
-        <v>0.0911</v>
-      </c>
-      <c r="E23">
-        <v>0.0287</v>
+        <v>-0.0751</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>-0.2077922077922078</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>-0.2077922077922078</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>-0.1883116883116883</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>-0.1883116883116883</v>
       </c>
       <c r="K23">
-        <v>5.25</v>
+        <v>-0.031</v>
       </c>
       <c r="L23">
-        <v>0.2364864864864865</v>
+        <v>-0.2012987012987013</v>
       </c>
       <c r="M23">
-        <v>3.8</v>
+        <v>0.014</v>
       </c>
       <c r="N23">
-        <v>0.1775700934579439</v>
+        <v>0.0903225806451613</v>
       </c>
       <c r="O23">
-        <v>0.7238095238095238</v>
+        <v>-0.4516129032258064</v>
       </c>
       <c r="P23">
-        <v>3.8</v>
+        <v>0.014</v>
       </c>
       <c r="Q23">
-        <v>0.1775700934579439</v>
+        <v>0.0903225806451613</v>
       </c>
       <c r="R23">
-        <v>0.7238095238095238</v>
+        <v>-0.4516129032258064</v>
       </c>
       <c r="S23">
         <v>0</v>
@@ -3288,55 +3267,55 @@
         <v>0</v>
       </c>
       <c r="U23">
-        <v>4.06</v>
+        <v>0.158</v>
       </c>
       <c r="V23">
-        <v>0.1897196261682243</v>
+        <v>1.019354838709677</v>
       </c>
       <c r="W23">
-        <v>0.1033464566929134</v>
+        <v>-0.0496</v>
       </c>
       <c r="X23">
-        <v>0.09252305325955615</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="Y23">
-        <v>0.01082340343335725</v>
+        <v>-0.1181626616768104</v>
       </c>
       <c r="Z23">
-        <v>0.1821060316470752</v>
+        <v>0.318840579710145</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>-0.06004140786749483</v>
       </c>
       <c r="AB23">
-        <v>0.06331240718492791</v>
+        <v>0.06856266167681045</v>
       </c>
       <c r="AC23">
-        <v>-0.06331240718492791</v>
+        <v>-0.1286040695443053</v>
       </c>
       <c r="AD23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="AE23">
         <v>0</v>
       </c>
       <c r="AF23">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="AG23">
-        <v>79.94</v>
+        <v>-0.158</v>
       </c>
       <c r="AH23">
-        <v>0.7969639468690701</v>
+        <v>0</v>
       </c>
       <c r="AI23">
-        <v>0.597864768683274</v>
+        <v>0</v>
       </c>
       <c r="AJ23">
-        <v>0.7888296822577462</v>
+        <v>52.66666666666662</v>
       </c>
       <c r="AK23">
-        <v>0.5858985634711228</v>
+        <v>-0.587360594795539</v>
       </c>
       <c r="AL23">
         <v>0</v>
@@ -3344,130 +3323,11 @@
       <c r="AM23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Trust Modaraba (KASE:TRSM)</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>-0.191</v>
-      </c>
-      <c r="E24">
-        <v>0.04559999999999999</v>
-      </c>
-      <c r="G24">
-        <v>0.006024096385542168</v>
-      </c>
-      <c r="H24">
-        <v>0.006024096385542168</v>
-      </c>
-      <c r="I24">
-        <v>-0.8493975903614457</v>
-      </c>
-      <c r="J24">
-        <v>-0.6673838209982788</v>
-      </c>
-      <c r="K24">
-        <v>0.1</v>
-      </c>
-      <c r="L24">
-        <v>0.6024096385542169</v>
-      </c>
-      <c r="M24">
-        <v>-0</v>
-      </c>
-      <c r="N24">
-        <v>-0</v>
-      </c>
-      <c r="O24">
-        <v>-0</v>
-      </c>
-      <c r="P24">
-        <v>-0</v>
-      </c>
-      <c r="Q24">
-        <v>-0</v>
-      </c>
-      <c r="R24">
-        <v>-0</v>
-      </c>
-      <c r="S24">
-        <v>0</v>
-      </c>
-      <c r="U24">
-        <v>0.059</v>
-      </c>
-      <c r="V24">
-        <v>0.1421686746987952</v>
-      </c>
-      <c r="W24">
-        <v>0.05319148936170214</v>
-      </c>
-      <c r="X24">
-        <v>0.03554488326449286</v>
-      </c>
-      <c r="Y24">
-        <v>0.01764660609720927</v>
-      </c>
-      <c r="Z24">
-        <v>0.08977825851811791</v>
-      </c>
-      <c r="AA24">
-        <v>-0.05991655721239279</v>
-      </c>
-      <c r="AB24">
-        <v>0.03554488326449286</v>
-      </c>
-      <c r="AC24">
-        <v>-0.09546144047688565</v>
-      </c>
-      <c r="AD24">
-        <v>0</v>
-      </c>
-      <c r="AE24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>0</v>
-      </c>
-      <c r="AG24">
-        <v>-0.059</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AI24">
-        <v>0</v>
-      </c>
-      <c r="AJ24">
-        <v>-0.1657303370786517</v>
-      </c>
-      <c r="AK24">
-        <v>-0.03170338527673294</v>
-      </c>
-      <c r="AL24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>0</v>
-      </c>
-      <c r="AN24">
-        <v>-0</v>
-      </c>
-      <c r="AP24">
-        <v>0.4275362318840579</v>
+      <c r="AN23">
+        <v>-0</v>
+      </c>
+      <c r="AP23">
+        <v>5.642857142857143</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ23"/>
+  <dimension ref="A1:AQ19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00176</v>
+        <v>0.0621</v>
       </c>
       <c r="E2">
-        <v>0.07625</v>
+        <v>0.0174</v>
       </c>
       <c r="G2">
-        <v>0.3159206275957545</v>
+        <v>0.3113621717415821</v>
       </c>
       <c r="H2">
-        <v>0.3132441162898015</v>
+        <v>0.3088448525857903</v>
       </c>
       <c r="I2">
-        <v>0.2963728657129672</v>
+        <v>0.332890285161914</v>
       </c>
       <c r="J2">
-        <v>0.2361372133158393</v>
+        <v>0.2614105628002764</v>
       </c>
       <c r="K2">
-        <v>11.959</v>
+        <v>7.892</v>
       </c>
       <c r="L2">
-        <v>0.2207475772958006</v>
+        <v>0.1589334622200741</v>
       </c>
       <c r="M2">
-        <v>6.4636</v>
+        <v>4.49</v>
       </c>
       <c r="N2">
-        <v>0.09511308621628384</v>
+        <v>0.07415481675997952</v>
       </c>
       <c r="O2">
-        <v>0.5404799732419099</v>
+        <v>0.5689305625950329</v>
       </c>
       <c r="P2">
-        <v>6.4636</v>
+        <v>4.49</v>
       </c>
       <c r="Q2">
-        <v>0.09511308621628384</v>
+        <v>0.07415481675997952</v>
       </c>
       <c r="R2">
-        <v>0.5404799732419099</v>
+        <v>0.5689305625950329</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.627</v>
+        <v>9.849</v>
       </c>
       <c r="V2">
-        <v>0.2152390482216696</v>
+        <v>0.1626616459396522</v>
       </c>
       <c r="W2">
-        <v>0.02853881278538813</v>
+        <v>0.04850574712643679</v>
       </c>
       <c r="X2">
-        <v>0.08441127901971202</v>
+        <v>0.111260666900187</v>
       </c>
       <c r="Y2">
-        <v>-0.05587246623432389</v>
+        <v>-0.0627549197737502</v>
       </c>
       <c r="Z2">
-        <v>0.1502836456440629</v>
+        <v>0.1584080084474063</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09404495170720109</v>
+        <v>0.1122491212805251</v>
       </c>
       <c r="AC2">
-        <v>-0.07315449841150433</v>
+        <v>-0.09290696383292771</v>
       </c>
       <c r="AD2">
-        <v>155.18</v>
+        <v>153.607</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>155.18</v>
+        <v>153.607</v>
       </c>
       <c r="AG2">
-        <v>140.553</v>
+        <v>143.758</v>
       </c>
       <c r="AH2">
-        <v>0.695447191635632</v>
+        <v>0.7172668522011991</v>
       </c>
       <c r="AI2">
-        <v>0.5032135885179876</v>
+        <v>0.57013955905278</v>
       </c>
       <c r="AJ2">
-        <v>0.6740827778044218</v>
+        <v>0.7036371734693379</v>
       </c>
       <c r="AK2">
-        <v>0.4784766690155949</v>
+        <v>0.5538292028000046</v>
       </c>
       <c r="AL2">
-        <v>10.209</v>
+        <v>14.307</v>
       </c>
       <c r="AM2">
-        <v>9.683999999999999</v>
+        <v>13.565</v>
       </c>
       <c r="AN2">
-        <v>9.228116079923883</v>
+        <v>8.533722222222222</v>
       </c>
       <c r="AO2">
-        <v>1.572729944166912</v>
+        <v>1.155378486055777</v>
       </c>
       <c r="AP2">
-        <v>8.358289724072312</v>
+        <v>7.986555555555556</v>
       </c>
       <c r="AQ2">
-        <v>1.657992565055762</v>
+        <v>1.218577220788795</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>First Punjab Modaraba (KASE:FPJM)</t>
+          <t>First Prudential Modaraba (KASE:PMI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,41 +721,44 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.262</v>
+      </c>
       <c r="G3">
-        <v>0.7738317757009345</v>
+        <v>0.6417910447761194</v>
       </c>
       <c r="H3">
-        <v>0.7738317757009345</v>
+        <v>0.6417910447761194</v>
       </c>
       <c r="I3">
-        <v>0.7635514018691588</v>
+        <v>0.6029850746268657</v>
       </c>
       <c r="J3">
-        <v>0.3817757009345794</v>
+        <v>0.6029850746268657</v>
       </c>
       <c r="K3">
-        <v>-0.031</v>
+        <v>0.395</v>
       </c>
       <c r="L3">
-        <v>-0.02897196261682243</v>
+        <v>0.5895522388059702</v>
       </c>
       <c r="M3">
-        <v>0.001</v>
+        <v>0.073</v>
       </c>
       <c r="N3">
-        <v>0.003846153846153846</v>
+        <v>0.07952069716775598</v>
       </c>
       <c r="O3">
-        <v>-0.03225806451612903</v>
+        <v>0.1848101265822785</v>
       </c>
       <c r="P3">
-        <v>0.001</v>
+        <v>0.073</v>
       </c>
       <c r="Q3">
-        <v>0.003846153846153846</v>
+        <v>0.07952069716775598</v>
       </c>
       <c r="R3">
-        <v>-0.03225806451612903</v>
+        <v>0.1848101265822785</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,58 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.391</v>
+        <v>0.267</v>
       </c>
       <c r="V3">
-        <v>1.503846153846154</v>
+        <v>0.2908496732026144</v>
+      </c>
+      <c r="W3">
+        <v>0.1211656441717791</v>
       </c>
       <c r="X3">
-        <v>0.7000691065708884</v>
+        <v>0.1034084064438415</v>
+      </c>
+      <c r="Y3">
+        <v>0.01775723772793768</v>
+      </c>
+      <c r="Z3">
+        <v>0.2043305885940836</v>
+      </c>
+      <c r="AA3">
+        <v>0.1232082952119549</v>
       </c>
       <c r="AB3">
-        <v>0.126096150873695</v>
+        <v>0.107738428934798</v>
+      </c>
+      <c r="AC3">
+        <v>0.01546986627715689</v>
       </c>
       <c r="AD3">
-        <v>7.77</v>
+        <v>0.521</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>7.77</v>
+        <v>0.521</v>
       </c>
       <c r="AG3">
-        <v>7.379</v>
+        <v>0.254</v>
       </c>
       <c r="AH3">
-        <v>0.9676214196762142</v>
+        <v>0.3620569840166782</v>
       </c>
       <c r="AI3">
-        <v>0.92643376654346</v>
+        <v>0.1658707418019739</v>
       </c>
       <c r="AJ3">
-        <v>0.9659641314308156</v>
+        <v>0.2167235494880546</v>
       </c>
       <c r="AK3">
-        <v>0.9228364182091046</v>
+        <v>0.08837856645789839</v>
       </c>
       <c r="AL3">
-        <v>0.78</v>
+        <v>0.121</v>
       </c>
       <c r="AM3">
-        <v>0.78</v>
+        <v>0.121</v>
       </c>
       <c r="AN3">
-        <v>9.418181818181818</v>
+        <v>1.074226804123711</v>
       </c>
       <c r="AO3">
-        <v>1.047435897435897</v>
+        <v>3.338842975206612</v>
       </c>
       <c r="AP3">
-        <v>8.944242424242423</v>
+        <v>0.5237113402061856</v>
       </c>
       <c r="AQ3">
-        <v>1.047435897435897</v>
+        <v>3.338842975206612</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +844,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>B.R.R. Guardian Modaraba (KASE:BRR)</t>
+          <t>First Habib Modaraba (KASE:FHAM)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,46 +853,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.327</v>
+        <v>0.453</v>
       </c>
       <c r="E4">
-        <v>0.349</v>
+        <v>0.171</v>
       </c>
       <c r="G4">
-        <v>0.812366737739872</v>
+        <v>0.7898550724637681</v>
       </c>
       <c r="H4">
-        <v>0.812366737739872</v>
+        <v>0.7898550724637681</v>
       </c>
       <c r="I4">
-        <v>0.7249466950959488</v>
+        <v>0.9057971014492753</v>
       </c>
       <c r="J4">
-        <v>0.6360965208799209</v>
+        <v>0.6057878703960122</v>
       </c>
       <c r="K4">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="L4">
-        <v>0.6140724946695095</v>
+        <v>0.1521739130434783</v>
       </c>
       <c r="M4">
-        <v>0.533</v>
+        <v>1.46</v>
       </c>
       <c r="N4">
-        <v>0.1055445544554456</v>
+        <v>0.2635379061371841</v>
       </c>
       <c r="O4">
-        <v>0.1850694444444445</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="P4">
-        <v>0.533</v>
+        <v>1.46</v>
       </c>
       <c r="Q4">
-        <v>0.1055445544554456</v>
+        <v>0.2635379061371841</v>
       </c>
       <c r="R4">
-        <v>0.1850694444444445</v>
+        <v>0.6952380952380952</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -883,73 +901,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.008999999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="V4">
-        <v>0.001782178217821782</v>
+        <v>0.4187725631768953</v>
       </c>
       <c r="W4">
-        <v>0.1531914893617021</v>
+        <v>0.1235294117647059</v>
       </c>
       <c r="X4">
-        <v>0.07278895963491754</v>
+        <v>0.39116243440092</v>
       </c>
       <c r="Y4">
-        <v>0.08040252972678459</v>
+        <v>-0.2676330226362141</v>
       </c>
       <c r="Z4">
-        <v>0.243042960045603</v>
+        <v>0.195356738391846</v>
       </c>
       <c r="AA4">
-        <v>0.1545987813093657</v>
+        <v>0.1183447425179073</v>
       </c>
       <c r="AB4">
-        <v>0.07802277446640681</v>
+        <v>0.1365271265209871</v>
       </c>
       <c r="AC4">
-        <v>0.07657600684295886</v>
+        <v>-0.01818238400307988</v>
       </c>
       <c r="AD4">
-        <v>1.01</v>
+        <v>51.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.01</v>
+        <v>51.9</v>
       </c>
       <c r="AG4">
-        <v>1.001</v>
+        <v>49.58</v>
       </c>
       <c r="AH4">
-        <v>0.1666666666666667</v>
+        <v>0.9035515320334262</v>
       </c>
       <c r="AI4">
-        <v>0.07107670654468684</v>
+        <v>0.7654867256637168</v>
       </c>
       <c r="AJ4">
-        <v>0.1654272021153529</v>
+        <v>0.8994920174165457</v>
       </c>
       <c r="AK4">
-        <v>0.07048799380325331</v>
+        <v>0.7571777642028099</v>
       </c>
       <c r="AL4">
-        <v>0.08</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="AM4">
-        <v>0.08</v>
+        <v>8.794</v>
       </c>
       <c r="AN4">
-        <v>0.2774725274725275</v>
+        <v>4.152</v>
       </c>
       <c r="AO4">
-        <v>42.5</v>
+        <v>1.367614879649891</v>
       </c>
       <c r="AP4">
-        <v>0.275</v>
+        <v>3.9664</v>
       </c>
       <c r="AQ4">
-        <v>42.5</v>
+        <v>1.421423697975893</v>
       </c>
     </row>
     <row r="5">
@@ -960,7 +978,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KASB Modaraba (KASE:KASBM)</t>
+          <t>First IBL Modaraba (KASE:FIBLM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,121 +987,109 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.123</v>
-      </c>
-      <c r="E5">
-        <v>0.0992</v>
+        <v>0.051</v>
       </c>
       <c r="G5">
-        <v>0.5957446808510639</v>
+        <v>0.4475524475524476</v>
       </c>
       <c r="H5">
-        <v>0.5957446808510639</v>
+        <v>0.4475524475524476</v>
       </c>
       <c r="I5">
-        <v>0.4680851063829788</v>
+        <v>0.3916083916083917</v>
       </c>
       <c r="J5">
-        <v>0.3343465045592706</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="K5">
-        <v>0.025</v>
+        <v>0.044</v>
       </c>
       <c r="L5">
-        <v>0.1773049645390071</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="M5">
-        <v>0.101</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.3519163763066203</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>4.04</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.101</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.3519163763066203</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>4.04</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>0.019</v>
+        <v>0.082</v>
       </c>
       <c r="V5">
-        <v>0.06620209059233449</v>
+        <v>0.3071161048689138</v>
       </c>
       <c r="W5">
-        <v>0.02853881278538813</v>
+        <v>0.05219454329774614</v>
       </c>
       <c r="X5">
-        <v>0.08512916064151593</v>
+        <v>0.08509667548689165</v>
       </c>
       <c r="Y5">
-        <v>-0.05659034785612781</v>
+        <v>-0.03290213218914551</v>
       </c>
       <c r="Z5">
-        <v>0.3759999999999999</v>
+        <v>0.2042857142857143</v>
       </c>
       <c r="AA5">
-        <v>0.1257142857142857</v>
+        <v>0.06285714285714286</v>
       </c>
       <c r="AB5">
-        <v>0.09469196297750399</v>
+        <v>0.08536056609250506</v>
       </c>
       <c r="AC5">
-        <v>0.03102232273678174</v>
+        <v>-0.0225034232353622</v>
       </c>
       <c r="AD5">
-        <v>0.225</v>
+        <v>0.002</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.225</v>
+        <v>0.002</v>
       </c>
       <c r="AG5">
-        <v>0.206</v>
+        <v>-0.08</v>
       </c>
       <c r="AH5">
-        <v>0.439453125</v>
+        <v>0.007434944237918215</v>
       </c>
       <c r="AI5">
-        <v>0.2497225305216426</v>
+        <v>0.002812939521800281</v>
       </c>
       <c r="AJ5">
-        <v>0.4178498985801217</v>
+        <v>-0.427807486631016</v>
       </c>
       <c r="AK5">
-        <v>0.2335600907029478</v>
+        <v>-0.1271860095389507</v>
       </c>
       <c r="AL5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>2.710843373493976</v>
-      </c>
-      <c r="AO5">
-        <v>2.64</v>
+        <v>0.02702702702702703</v>
       </c>
       <c r="AP5">
-        <v>2.481927710843374</v>
-      </c>
-      <c r="AQ5">
-        <v>2.64</v>
+        <v>-1.081081081081081</v>
       </c>
     </row>
     <row r="6">
@@ -1094,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>First Prudential Modaraba (KASE:PMI)</t>
+          <t>OLP Modaraba (KASE:OLPM)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1103,46 +1109,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.106</v>
+        <v>-0.018</v>
       </c>
       <c r="E6">
-        <v>0.0775</v>
+        <v>0.0455</v>
       </c>
       <c r="G6">
-        <v>0.4483985765124555</v>
+        <v>0.4125200642054574</v>
       </c>
       <c r="H6">
-        <v>0.4483985765124555</v>
+        <v>0.4125200642054574</v>
       </c>
       <c r="I6">
-        <v>0.4270462633451957</v>
+        <v>0.4622792937399678</v>
       </c>
       <c r="J6">
-        <v>0.360204239517252</v>
+        <v>0.3442505378914654</v>
       </c>
       <c r="K6">
-        <v>0.097</v>
+        <v>0.421</v>
       </c>
       <c r="L6">
-        <v>0.3451957295373665</v>
+        <v>0.06757624398073836</v>
       </c>
       <c r="M6">
-        <v>0.031</v>
+        <v>0.32</v>
       </c>
       <c r="N6">
-        <v>0.04518950437317784</v>
+        <v>0.1624365482233503</v>
       </c>
       <c r="O6">
-        <v>0.3195876288659794</v>
+        <v>0.7600950118764846</v>
       </c>
       <c r="P6">
-        <v>0.031</v>
+        <v>0.32</v>
       </c>
       <c r="Q6">
-        <v>0.04518950437317784</v>
+        <v>0.1624365482233503</v>
       </c>
       <c r="R6">
-        <v>0.3195876288659794</v>
+        <v>0.7600950118764846</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1151,73 +1157,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.443</v>
+        <v>1.2</v>
       </c>
       <c r="V6">
-        <v>0.6457725947521865</v>
+        <v>0.6091370558375634</v>
       </c>
       <c r="W6">
-        <v>0.037890625</v>
+        <v>0.07558348294434469</v>
       </c>
       <c r="X6">
-        <v>0.07530872037087352</v>
+        <v>0.3387909569549424</v>
       </c>
       <c r="Y6">
-        <v>-0.03741809537087352</v>
+        <v>-0.2632074740105977</v>
       </c>
       <c r="Z6">
-        <v>0.1907671418873048</v>
+        <v>0.2438356164383562</v>
       </c>
       <c r="AA6">
-        <v>0.06871513326839634</v>
+        <v>0.08394054211600116</v>
       </c>
       <c r="AB6">
-        <v>0.08295100444535147</v>
+        <v>0.1355192898038359</v>
       </c>
       <c r="AC6">
-        <v>-0.01423587117695513</v>
+        <v>-0.05157874768783471</v>
       </c>
       <c r="AD6">
-        <v>0.219</v>
+        <v>15.3</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.219</v>
+        <v>15.3</v>
       </c>
       <c r="AG6">
-        <v>-0.224</v>
+        <v>14.1</v>
       </c>
       <c r="AH6">
-        <v>0.2419889502762431</v>
+        <v>0.885929357266937</v>
       </c>
       <c r="AI6">
-        <v>0.09869310500225327</v>
+        <v>0.7964601769911505</v>
       </c>
       <c r="AJ6">
-        <v>-0.4848484848484848</v>
+        <v>0.8774113254511513</v>
       </c>
       <c r="AK6">
-        <v>-0.1261261261261261</v>
+        <v>0.7828983897834536</v>
       </c>
       <c r="AL6">
-        <v>0.025</v>
+        <v>2.51</v>
       </c>
       <c r="AM6">
-        <v>0.025</v>
+        <v>2.51</v>
       </c>
       <c r="AN6">
-        <v>1.598540145985401</v>
+        <v>4.358974358974359</v>
       </c>
       <c r="AO6">
-        <v>4.8</v>
+        <v>1.147410358565737</v>
       </c>
       <c r="AP6">
-        <v>-1.635036496350365</v>
+        <v>4.017094017094018</v>
       </c>
       <c r="AQ6">
-        <v>4.8</v>
+        <v>1.147410358565737</v>
       </c>
     </row>
     <row r="7">
@@ -1237,46 +1243,46 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0764</v>
+        <v>0.0537</v>
       </c>
       <c r="E7">
-        <v>0.272</v>
+        <v>-0.0489</v>
       </c>
       <c r="G7">
-        <v>0.7333333333333332</v>
+        <v>0.6320541760722348</v>
       </c>
       <c r="H7">
-        <v>0.7333333333333332</v>
+        <v>0.6320541760722348</v>
       </c>
       <c r="I7">
-        <v>0.7207207207207207</v>
+        <v>0.6354401805869074</v>
       </c>
       <c r="J7">
-        <v>0.6326526027274156</v>
+        <v>0.484035661024684</v>
       </c>
       <c r="K7">
-        <v>0.703</v>
+        <v>0.211</v>
       </c>
       <c r="L7">
-        <v>0.6333333333333332</v>
+        <v>0.2381489841986456</v>
       </c>
       <c r="M7">
-        <v>0.1016</v>
+        <v>0.39</v>
       </c>
       <c r="N7">
-        <v>0.1369272237196766</v>
+        <v>0.2785714285714286</v>
       </c>
       <c r="O7">
-        <v>0.1445234708392603</v>
+        <v>1.848341232227488</v>
       </c>
       <c r="P7">
-        <v>0.1016</v>
+        <v>0.39</v>
       </c>
       <c r="Q7">
-        <v>0.1369272237196766</v>
+        <v>0.2785714285714286</v>
       </c>
       <c r="R7">
-        <v>0.1445234708392603</v>
+        <v>1.848341232227488</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,73 +1291,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.129</v>
+        <v>0.284</v>
       </c>
       <c r="V7">
-        <v>0.1738544474393531</v>
+        <v>0.2028571428571428</v>
       </c>
       <c r="W7">
-        <v>0.1555309734513274</v>
+        <v>0.04850574712643679</v>
       </c>
       <c r="X7">
-        <v>0.1408995674287781</v>
+        <v>0.1205846293075795</v>
       </c>
       <c r="Y7">
-        <v>0.01463140602254936</v>
+        <v>-0.07207888218114269</v>
       </c>
       <c r="Z7">
-        <v>0.1365313653136532</v>
+        <v>0.1138378517281254</v>
       </c>
       <c r="AA7">
-        <v>0.08637692361961027</v>
+        <v>0.05510157981085313</v>
       </c>
       <c r="AB7">
-        <v>0.1145788222232604</v>
+        <v>0.125769398601267</v>
       </c>
       <c r="AC7">
-        <v>-0.02820189860365008</v>
+        <v>-0.07066781879041382</v>
       </c>
       <c r="AD7">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG7">
-        <v>2.411</v>
+        <v>1.246</v>
       </c>
       <c r="AH7">
-        <v>0.7739183424741012</v>
+        <v>0.522184300341297</v>
       </c>
       <c r="AI7">
-        <v>0.3907692307692308</v>
+        <v>0.3415178571428571</v>
       </c>
       <c r="AJ7">
-        <v>0.7646685696162385</v>
+        <v>0.4708994708994709</v>
       </c>
       <c r="AK7">
-        <v>0.378433526918851</v>
+        <v>0.2969494756911344</v>
       </c>
       <c r="AL7">
-        <v>0.349</v>
+        <v>0.322</v>
       </c>
       <c r="AM7">
-        <v>0.349</v>
+        <v>0.322</v>
       </c>
       <c r="AN7">
-        <v>3.17103620474407</v>
+        <v>2.679509632224168</v>
       </c>
       <c r="AO7">
-        <v>2.292263610315187</v>
+        <v>1.748447204968944</v>
       </c>
       <c r="AP7">
-        <v>3.009987515605493</v>
+        <v>2.182136602451839</v>
       </c>
       <c r="AQ7">
-        <v>2.292263610315187</v>
+        <v>1.748447204968944</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>First Habib Modaraba (KASE:FHAM)</t>
+          <t>UDL Modaraba Management (Private) Limited (KASE:FUDLM)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,46 +1377,43 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.289</v>
-      </c>
-      <c r="E8">
-        <v>0.075</v>
+        <v>-0.0243</v>
       </c>
       <c r="G8">
-        <v>0.764018691588785</v>
+        <v>0.1350210970464135</v>
       </c>
       <c r="H8">
-        <v>0.764018691588785</v>
+        <v>0.1350210970464135</v>
       </c>
       <c r="I8">
-        <v>0.8691588785046729</v>
+        <v>0.05907172995780591</v>
       </c>
       <c r="J8">
-        <v>0.6754395691430382</v>
+        <v>0.02953586497890296</v>
       </c>
       <c r="K8">
-        <v>1.83</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="L8">
-        <v>0.2137850467289719</v>
+        <v>-0.0379746835443038</v>
       </c>
       <c r="M8">
-        <v>1.22</v>
+        <v>0.11</v>
       </c>
       <c r="N8">
-        <v>0.1826347305389222</v>
+        <v>0.1320528211284514</v>
       </c>
       <c r="O8">
-        <v>0.6666666666666666</v>
+        <v>-12.22222222222222</v>
       </c>
       <c r="P8">
-        <v>1.22</v>
+        <v>0.11</v>
       </c>
       <c r="Q8">
-        <v>0.1826347305389222</v>
+        <v>0.1320528211284514</v>
       </c>
       <c r="R8">
-        <v>0.6666666666666666</v>
+        <v>-12.22222222222222</v>
       </c>
       <c r="S8">
         <v>0</v>
@@ -1419,73 +1422,73 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>1.06</v>
+        <v>0.135</v>
       </c>
       <c r="V8">
-        <v>0.1586826347305389</v>
+        <v>0.1620648259303722</v>
       </c>
       <c r="W8">
-        <v>0.07854077253218884</v>
+        <v>-0.00371900826446281</v>
       </c>
       <c r="X8">
-        <v>0.2416004598118835</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="Y8">
-        <v>-0.1630596872796947</v>
+        <v>-0.08857076429978086</v>
       </c>
       <c r="Z8">
-        <v>0.122373123659757</v>
+        <v>0.1119508738781294</v>
       </c>
       <c r="AA8">
-        <v>0.08265564991943398</v>
+        <v>0.003306565895134624</v>
       </c>
       <c r="AB8">
-        <v>0.1215504364820487</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="AC8">
-        <v>-0.03889478656261476</v>
+        <v>-0.08154519014018342</v>
       </c>
       <c r="AD8">
-        <v>54.7</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>54.7</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>53.64</v>
+        <v>-0.135</v>
       </c>
       <c r="AH8">
-        <v>0.8911697621375041</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.7629009762900977</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.8892572944297082</v>
+        <v>-0.1934097421203439</v>
       </c>
       <c r="AK8">
-        <v>0.7593431483578709</v>
+        <v>-0.08571428571428573</v>
       </c>
       <c r="AL8">
-        <v>5.51</v>
+        <v>0.001</v>
       </c>
       <c r="AM8">
-        <v>5.253</v>
+        <v>0.001</v>
       </c>
       <c r="AN8">
-        <v>7.715091678420311</v>
+        <v>0</v>
       </c>
       <c r="AO8">
-        <v>1.3502722323049</v>
+        <v>14</v>
       </c>
       <c r="AP8">
-        <v>7.565585331452751</v>
+        <v>-4.500000000000001</v>
       </c>
       <c r="AQ8">
-        <v>1.416333523700742</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -1496,7 +1499,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First IBL Modaraba (KASE:FIBLM)</t>
+          <t>Trust Modaraba (KASE:TRSM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1505,25 +1508,28 @@
         </is>
       </c>
       <c r="D9">
-        <v>-0.0185</v>
+        <v>0.169</v>
+      </c>
+      <c r="E9">
+        <v>-0.0167</v>
       </c>
       <c r="G9">
-        <v>0.3703703703703703</v>
+        <v>0.01315789473684211</v>
       </c>
       <c r="H9">
-        <v>0.3703703703703703</v>
+        <v>0.01315789473684211</v>
       </c>
       <c r="I9">
-        <v>0.1703703703703704</v>
+        <v>0.07894736842105264</v>
       </c>
       <c r="J9">
-        <v>0.1703703703703704</v>
+        <v>0.03947368421052632</v>
       </c>
       <c r="K9">
-        <v>-0.004</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="L9">
-        <v>-0.02962962962962963</v>
+        <v>0.05921052631578947</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1532,7 +1538,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1541,61 +1547,61 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>0.037</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>0.1720930232558139</v>
       </c>
       <c r="W9">
-        <v>-0.003508771929824562</v>
+        <v>0.006382978723404255</v>
       </c>
       <c r="X9">
-        <v>0.06867941023918911</v>
+        <v>0.08606837917150692</v>
       </c>
       <c r="Y9">
-        <v>-0.07218818216901367</v>
+        <v>-0.07968540044810267</v>
       </c>
       <c r="Z9">
-        <v>0.1681195516811956</v>
+        <v>0.1098265895953757</v>
       </c>
       <c r="AA9">
-        <v>0.02864259028642591</v>
+        <v>0.004335260115606937</v>
       </c>
       <c r="AB9">
-        <v>0.06888935770284112</v>
+        <v>0.08711948348613971</v>
       </c>
       <c r="AC9">
-        <v>-0.04024676741641521</v>
+        <v>-0.08278422337053278</v>
       </c>
       <c r="AD9">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.003</v>
+        <v>0.008</v>
       </c>
       <c r="AG9">
-        <v>0.003</v>
+        <v>-0.029</v>
       </c>
       <c r="AH9">
-        <v>0.005494505494505494</v>
+        <v>0.03587443946188341</v>
       </c>
       <c r="AI9">
-        <v>0.003592814371257485</v>
+        <v>0.0070298769771529</v>
       </c>
       <c r="AJ9">
-        <v>0.005494505494505494</v>
+        <v>-0.1559139784946237</v>
       </c>
       <c r="AK9">
-        <v>0.003592814371257485</v>
+        <v>-0.02633969118982743</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1604,10 +1610,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>0.06122448979591837</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="AP9">
-        <v>0.06122448979591837</v>
+        <v>-1.705882352941176</v>
       </c>
     </row>
     <row r="10">
@@ -1618,7 +1624,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>OLP Modaraba (KASE:OLPM)</t>
+          <t>First Punjab Modaraba (KASE:FPJM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1626,122 +1632,113 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D10">
-        <v>-0.0361</v>
-      </c>
-      <c r="E10">
-        <v>-0.0344</v>
-      </c>
       <c r="G10">
-        <v>0.3681948424068767</v>
+        <v>0.6242707117852976</v>
       </c>
       <c r="H10">
-        <v>0.3681948424068767</v>
+        <v>0.6242707117852976</v>
       </c>
       <c r="I10">
-        <v>0.3896848137535817</v>
+        <v>0.6137689614935823</v>
       </c>
       <c r="J10">
-        <v>0.2727196935457685</v>
+        <v>0.6137689614935823</v>
       </c>
       <c r="K10">
-        <v>0.457</v>
+        <v>-0.33</v>
       </c>
       <c r="L10">
-        <v>0.0654727793696275</v>
+        <v>-0.3850641773628938</v>
       </c>
       <c r="M10">
-        <v>0.57</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.2235294117647059</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>1.2472647702407</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>0.57</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.2235294117647059</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>1.2472647702407</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>3.78</v>
+        <v>0.212</v>
       </c>
       <c r="V10">
-        <v>1.482352941176471</v>
+        <v>0.8833333333333333</v>
       </c>
       <c r="W10">
-        <v>0.07359098228663447</v>
+        <v>-0.3654485049833887</v>
       </c>
       <c r="X10">
-        <v>0.2384432658752325</v>
+        <v>0.9608520969854744</v>
       </c>
       <c r="Y10">
-        <v>-0.164852283588598</v>
+        <v>-1.326300601968863</v>
       </c>
       <c r="Z10">
-        <v>0.2441413081497027</v>
+        <v>0.09104430043556783</v>
       </c>
       <c r="AA10">
-        <v>0.06658214274044996</v>
+        <v>0.05588016572824817</v>
       </c>
       <c r="AB10">
-        <v>0.1214434804672813</v>
+        <v>0.145790131493689</v>
       </c>
       <c r="AC10">
-        <v>-0.05486133772683133</v>
+        <v>-0.08990996576544083</v>
       </c>
       <c r="AD10">
-        <v>20.5</v>
+        <v>6.43</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>20.5</v>
+        <v>6.43</v>
       </c>
       <c r="AG10">
-        <v>16.72</v>
+        <v>6.218</v>
       </c>
       <c r="AH10">
-        <v>0.8893709327548807</v>
+        <v>0.9640179910044977</v>
       </c>
       <c r="AI10">
-        <v>0.8134920634920635</v>
+        <v>0.9993783027665527</v>
       </c>
       <c r="AJ10">
-        <v>0.8676699532952776</v>
+        <v>0.9628367915763394</v>
       </c>
       <c r="AK10">
-        <v>0.7805788982259571</v>
+        <v>0.9993571198971393</v>
       </c>
       <c r="AL10">
-        <v>2.09</v>
+        <v>0.893</v>
       </c>
       <c r="AM10">
-        <v>2.09</v>
+        <v>0.893</v>
       </c>
       <c r="AN10">
-        <v>7.454545454545454</v>
+        <v>12.06378986866792</v>
       </c>
       <c r="AO10">
-        <v>1.301435406698565</v>
+        <v>0.5890257558790594</v>
       </c>
       <c r="AP10">
-        <v>6.079999999999999</v>
+        <v>11.66604127579737</v>
       </c>
       <c r="AQ10">
-        <v>1.301435406698565</v>
+        <v>0.5890257558790594</v>
       </c>
     </row>
     <row r="11">
@@ -1761,79 +1758,76 @@
         </is>
       </c>
       <c r="D11">
-        <v>0.052</v>
+        <v>0.129</v>
       </c>
       <c r="E11">
-        <v>-0.0147</v>
+        <v>1.007</v>
       </c>
       <c r="G11">
-        <v>0.189297124600639</v>
+        <v>0.07734082397003746</v>
       </c>
       <c r="H11">
-        <v>0.1661341853035144</v>
+        <v>0.05393258426966292</v>
       </c>
       <c r="I11">
-        <v>0.0009584664536741214</v>
+        <v>-0.06779026217228465</v>
       </c>
       <c r="J11">
-        <v>0.0008196755321355961</v>
+        <v>-0.06515064134433729</v>
       </c>
       <c r="K11">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="L11">
-        <v>0.2108626198083067</v>
+        <v>0.2041198501872659</v>
       </c>
       <c r="M11">
-        <v>0.6860000000000001</v>
+        <v>-0</v>
       </c>
       <c r="N11">
-        <v>0.02398601398601399</v>
+        <v>-0</v>
       </c>
       <c r="O11">
-        <v>0.5196969696969698</v>
+        <v>-0</v>
       </c>
       <c r="P11">
-        <v>0.6860000000000001</v>
+        <v>-0</v>
       </c>
       <c r="Q11">
-        <v>0.02398601398601399</v>
+        <v>-0</v>
       </c>
       <c r="R11">
-        <v>0.5196969696969698</v>
+        <v>-0</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
       <c r="U11">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="V11">
-        <v>0.05979020979020978</v>
+        <v>0.05167785234899329</v>
       </c>
       <c r="W11">
-        <v>0.0227979274611399</v>
+        <v>0.02427616926503341</v>
       </c>
       <c r="X11">
-        <v>0.06856266167681045</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="Y11">
-        <v>-0.04576473421567055</v>
+        <v>-0.06057558677028464</v>
       </c>
       <c r="Z11">
-        <v>0.11254944264653</v>
+        <v>0.12363973141931</v>
       </c>
       <c r="AA11">
-        <v>9.225402429285924e-05</v>
+        <v>-0.008055207797609657</v>
       </c>
       <c r="AB11">
-        <v>0.06856266167681045</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="AC11">
-        <v>-0.06847040765251759</v>
+        <v>-0.09290696383292771</v>
       </c>
       <c r="AD11">
         <v>0</v>
@@ -1845,7 +1839,7 @@
         <v>0</v>
       </c>
       <c r="AG11">
-        <v>-1.71</v>
+        <v>-1.54</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1854,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-0.06359241353663071</v>
+        <v>-0.05449398443029016</v>
       </c>
       <c r="AK11">
-        <v>-0.03959249826348692</v>
+        <v>-0.04392470051340559</v>
       </c>
       <c r="AL11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-0.002</v>
+        <v>-0.006</v>
       </c>
       <c r="AN11">
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>-2.326530612244898</v>
+        <v>-4.767801857585139</v>
       </c>
       <c r="AQ11">
-        <v>-3</v>
+        <v>60.33333333333333</v>
       </c>
     </row>
     <row r="12">
@@ -1883,7 +1877,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Habib Metro Modaraba (KASE:HMM)</t>
+          <t>Grays Leasing Limited (KASE:GRYL)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1891,6 +1885,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D12">
+        <v>0.226</v>
+      </c>
       <c r="G12">
         <v>0</v>
       </c>
@@ -1904,85 +1901,82 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0.105</v>
+        <v>0.016</v>
       </c>
       <c r="L12">
-        <v>0.4838709677419354</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M12">
-        <v>0.052</v>
+        <v>-0</v>
       </c>
       <c r="N12">
-        <v>0.0761346998535871</v>
+        <v>-0</v>
       </c>
       <c r="O12">
-        <v>0.4952380952380953</v>
+        <v>-0</v>
       </c>
       <c r="P12">
-        <v>0.052</v>
+        <v>-0</v>
       </c>
       <c r="Q12">
-        <v>0.0761346998535871</v>
+        <v>-0</v>
       </c>
       <c r="R12">
-        <v>0.4952380952380953</v>
+        <v>-0</v>
       </c>
       <c r="S12">
         <v>0</v>
       </c>
-      <c r="T12">
-        <v>0</v>
-      </c>
       <c r="U12">
-        <v>0.612</v>
+        <v>0.019</v>
       </c>
       <c r="V12">
-        <v>0.8960468521229867</v>
+        <v>0.07630522088353414</v>
       </c>
       <c r="W12">
-        <v>0.05440414507772021</v>
+        <v>0.05970149253731343</v>
       </c>
       <c r="X12">
-        <v>0.06856266167681045</v>
+        <v>0.1031041568510833</v>
       </c>
       <c r="Y12">
-        <v>-0.01415851659909025</v>
+        <v>-0.04340266431376983</v>
       </c>
       <c r="Z12">
-        <v>0.1202882483370288</v>
+        <v>0.2464985994397759</v>
       </c>
       <c r="AA12">
         <v>0</v>
       </c>
       <c r="AB12">
-        <v>0.06856266167681045</v>
+        <v>0.1068187402212456</v>
       </c>
       <c r="AC12">
-        <v>-0.06856266167681045</v>
+        <v>-0.1068187402212456</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AE12">
         <v>0</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>0.139</v>
       </c>
       <c r="AG12">
-        <v>-0.612</v>
+        <v>0.12</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>0.3582474226804124</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>0.3808219178082192</v>
       </c>
       <c r="AJ12">
-        <v>-8.619718309859147</v>
+        <v>0.3252032520325204</v>
       </c>
       <c r="AK12">
-        <v>-0.7391304347826088</v>
+        <v>0.3468208092485549</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -1999,7 +1993,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>First Fidelity Leasing Modaraba (KASE:FFLM)</t>
+          <t>Next Capital Limited (KASE:NEXT)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2008,25 +2002,25 @@
         </is>
       </c>
       <c r="D13">
-        <v>0.541</v>
+        <v>-0.16</v>
       </c>
       <c r="G13">
-        <v>-0.08888888888888889</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>-0.08888888888888889</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>-0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>-0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>-0.027</v>
+        <v>-0.34</v>
       </c>
       <c r="L13">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
       <c r="M13">
         <v>-0</v>
@@ -2050,67 +2044,61 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>0.973</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>0.8610619469026549</v>
       </c>
       <c r="W13">
-        <v>-0.01377551020408163</v>
+        <v>-0.132295719844358</v>
       </c>
       <c r="X13">
-        <v>0.06856266167681045</v>
+        <v>0.1033702674888123</v>
       </c>
       <c r="Y13">
-        <v>-0.08233817188089208</v>
+        <v>-0.2356659873331703</v>
       </c>
       <c r="Z13">
-        <v>0.04591836734693878</v>
+        <v>0.1432785503581964</v>
       </c>
       <c r="AA13">
-        <v>-0.004591836734693877</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>0.06856266167681045</v>
+        <v>0.1070232046921872</v>
       </c>
       <c r="AC13">
-        <v>-0.07315449841150433</v>
+        <v>-0.1070232046921872</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AE13">
         <v>0</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>-0.333</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>0.3615819209039548</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>0.3004694835680751</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>-0.4178168130489335</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>-0.2878133102852203</v>
       </c>
       <c r="AL13">
         <v>0</v>
       </c>
       <c r="AM13">
         <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>-0</v>
-      </c>
-      <c r="AP13">
-        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -2121,7 +2109,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UDL Modaraba Management (Private) Limited (KASE:FUDLM)</t>
+          <t>First Dawood Investment Bank Limited (KASE:FDIBL)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2130,115 +2118,106 @@
         </is>
       </c>
       <c r="D14">
-        <v>-0.249</v>
+        <v>-0.0742</v>
       </c>
       <c r="E14">
-        <v>0.225</v>
+        <v>-0.635</v>
       </c>
       <c r="G14">
-        <v>-0.009569377990430623</v>
+        <v>0</v>
       </c>
       <c r="H14">
-        <v>-0.009569377990430623</v>
+        <v>0</v>
       </c>
       <c r="I14">
-        <v>-0.1196172248803828</v>
+        <v>0</v>
       </c>
       <c r="J14">
-        <v>-0.1126588821588093</v>
+        <v>0</v>
       </c>
       <c r="K14">
-        <v>0.34</v>
+        <v>0.002</v>
       </c>
       <c r="L14">
-        <v>1.626794258373206</v>
+        <v>0.008064516129032258</v>
       </c>
       <c r="M14">
-        <v>0.323</v>
+        <v>-0</v>
       </c>
       <c r="N14">
-        <v>0.3336776859504132</v>
+        <v>-0</v>
       </c>
       <c r="O14">
-        <v>0.95</v>
+        <v>-0</v>
       </c>
       <c r="P14">
-        <v>0.323</v>
+        <v>-0</v>
       </c>
       <c r="Q14">
-        <v>0.3336776859504132</v>
+        <v>-0</v>
       </c>
       <c r="R14">
-        <v>0.95</v>
+        <v>-0</v>
       </c>
       <c r="S14">
         <v>0</v>
       </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
       <c r="U14">
-        <v>0.303</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="V14">
-        <v>0.3130165289256198</v>
+        <v>0.06461538461538462</v>
       </c>
       <c r="W14">
-        <v>0.08740359897172237</v>
+        <v>0.0008333333333333334</v>
       </c>
       <c r="X14">
-        <v>0.06856266167681045</v>
+        <v>0.111260666900187</v>
       </c>
       <c r="Y14">
-        <v>0.01884093729491192</v>
+        <v>-0.1104273335668536</v>
       </c>
       <c r="Z14">
-        <v>0.06541471048513302</v>
+        <v>0.06531472214906506</v>
       </c>
       <c r="AA14">
-        <v>-0.007369548159997225</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>0.06856266167681045</v>
+        <v>0.1122491212805251</v>
       </c>
       <c r="AC14">
-        <v>-0.07593220983680768</v>
+        <v>-0.1122491212805251</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AE14">
         <v>0</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG14">
-        <v>-0.303</v>
+        <v>0.9660000000000001</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>0.4468085106382979</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>0.3409090909090909</v>
       </c>
       <c r="AJ14">
-        <v>-0.4556390977443608</v>
+        <v>0.4263018534863195</v>
       </c>
       <c r="AK14">
-        <v>-0.1431270666036845</v>
+        <v>0.3224299065420561</v>
       </c>
       <c r="AL14">
         <v>0</v>
       </c>
       <c r="AM14">
         <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>-0</v>
-      </c>
-      <c r="AP14">
-        <v>30.3</v>
       </c>
     </row>
     <row r="15">
@@ -2249,7 +2228,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Next Capital Limited (KASE:NEXT)</t>
+          <t>First Paramount Modaraba (KASE:FPRM)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2258,10 +2237,10 @@
         </is>
       </c>
       <c r="D15">
-        <v>-0.0202</v>
+        <v>0.128</v>
       </c>
       <c r="E15">
-        <v>-0.125</v>
+        <v>0.145</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2276,82 +2255,85 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>0.133</v>
+        <v>0.054</v>
       </c>
       <c r="L15">
-        <v>0.09300699300699301</v>
+        <v>0.03776223776223776</v>
       </c>
       <c r="M15">
-        <v>-0</v>
+        <v>0.007</v>
       </c>
       <c r="N15">
-        <v>-0</v>
+        <v>0.01590909090909091</v>
       </c>
       <c r="O15">
-        <v>-0</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="P15">
-        <v>-0</v>
+        <v>0.007</v>
       </c>
       <c r="Q15">
-        <v>-0</v>
+        <v>0.01590909090909091</v>
       </c>
       <c r="R15">
-        <v>-0</v>
+        <v>0.1296296296296296</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
+      <c r="T15">
+        <v>0</v>
+      </c>
       <c r="U15">
-        <v>1.17</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="V15">
-        <v>0.9590163934426229</v>
+        <v>0.1954545454545454</v>
       </c>
       <c r="W15">
-        <v>0.04836363636363637</v>
+        <v>0.05702217529039071</v>
       </c>
       <c r="X15">
-        <v>0.08226348825411661</v>
+        <v>0.1259456218811065</v>
       </c>
       <c r="Y15">
-        <v>-0.03389985189048025</v>
+        <v>-0.06892344659071581</v>
       </c>
       <c r="Z15">
-        <v>0.6559633027522936</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="AA15">
         <v>0</v>
       </c>
       <c r="AB15">
-        <v>0.09088871602759331</v>
+        <v>0.1200549133248292</v>
       </c>
       <c r="AC15">
-        <v>-0.09088871602759331</v>
+        <v>-0.1200549133248292</v>
       </c>
       <c r="AD15">
-        <v>0.791</v>
+        <v>0.553</v>
       </c>
       <c r="AE15">
         <v>0</v>
       </c>
       <c r="AF15">
-        <v>0.791</v>
+        <v>0.553</v>
       </c>
       <c r="AG15">
-        <v>-0.3789999999999999</v>
+        <v>0.4670000000000001</v>
       </c>
       <c r="AH15">
-        <v>0.3933366484336151</v>
+        <v>0.5568982880161127</v>
       </c>
       <c r="AI15">
-        <v>0.2653471989265347</v>
+        <v>0.40691685062546</v>
       </c>
       <c r="AJ15">
-        <v>-0.4506539833531508</v>
+        <v>0.5148842337375965</v>
       </c>
       <c r="AK15">
-        <v>-0.2092766427388183</v>
+        <v>0.3668499607227023</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2368,7 +2350,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grays Leasing Limited (KASE:GRYL)</t>
+          <t>OLP Financial Services Pakistan Limited (KASE:OLPL)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2377,7 +2359,10 @@
         </is>
       </c>
       <c r="D16">
-        <v>0.122</v>
+        <v>0.021</v>
+      </c>
+      <c r="E16">
+        <v>-0.0107</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2392,82 +2377,85 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>-0.008999999999999999</v>
+        <v>4.66</v>
       </c>
       <c r="L16">
-        <v>-0.09999999999999999</v>
+        <v>0.2757396449704143</v>
       </c>
       <c r="M16">
-        <v>-0</v>
+        <v>2.13</v>
       </c>
       <c r="N16">
-        <v>-0</v>
+        <v>0.1489510489510489</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>0.4570815450643776</v>
       </c>
       <c r="P16">
-        <v>-0</v>
+        <v>2.13</v>
       </c>
       <c r="Q16">
-        <v>-0</v>
+        <v>0.1489510489510489</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>0.4570815450643776</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
       <c r="U16">
-        <v>0.13</v>
+        <v>2.45</v>
       </c>
       <c r="V16">
-        <v>0.4452054794520549</v>
+        <v>0.1713286713286713</v>
       </c>
       <c r="W16">
-        <v>-0.02432432432432432</v>
+        <v>0.1156327543424318</v>
       </c>
       <c r="X16">
-        <v>0.08441127901971202</v>
+        <v>0.2323300894365341</v>
       </c>
       <c r="Y16">
-        <v>-0.1087356033440363</v>
+        <v>-0.1166973350941023</v>
       </c>
       <c r="Z16">
-        <v>0.1339285714285714</v>
+        <v>0.142712379665597</v>
       </c>
       <c r="AA16">
         <v>0</v>
       </c>
       <c r="AB16">
-        <v>0.09404495170720109</v>
+        <v>0.1316645076674458</v>
       </c>
       <c r="AC16">
-        <v>-0.09404495170720109</v>
+        <v>-0.1316645076674458</v>
       </c>
       <c r="AD16">
-        <v>0.219</v>
+        <v>64.5</v>
       </c>
       <c r="AE16">
         <v>0</v>
       </c>
       <c r="AF16">
-        <v>0.219</v>
+        <v>64.5</v>
       </c>
       <c r="AG16">
-        <v>0.089</v>
+        <v>62.05</v>
       </c>
       <c r="AH16">
-        <v>0.4285714285714285</v>
+        <v>0.8185279187817259</v>
       </c>
       <c r="AI16">
-        <v>0.4496919917864476</v>
+        <v>0.627431906614786</v>
       </c>
       <c r="AJ16">
-        <v>0.2335958005249344</v>
+        <v>0.8127046496398167</v>
       </c>
       <c r="AK16">
-        <v>0.2492997198879552</v>
+        <v>0.6183358246138515</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -2484,7 +2472,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Trust Modaraba (KASE:TRSM)</t>
+          <t>SME Leasing Limited (KASE:SLL)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2493,25 +2481,25 @@
         </is>
       </c>
       <c r="D17">
-        <v>-0.178</v>
+        <v>0.229</v>
       </c>
       <c r="G17">
-        <v>-1.129032258064516</v>
+        <v>0</v>
       </c>
       <c r="H17">
-        <v>-1.129032258064516</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>-0.2661290322580646</v>
+        <v>0</v>
       </c>
       <c r="J17">
-        <v>-0.2661290322580646</v>
+        <v>0</v>
       </c>
       <c r="K17">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L17">
-        <v>-0.04032258064516129</v>
+        <v>0.02242152466367713</v>
       </c>
       <c r="M17">
         <v>-0</v>
@@ -2520,7 +2508,7 @@
         <v>-0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P17">
         <v>-0</v>
@@ -2529,73 +2517,67 @@
         <v>-0</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S17">
         <v>0</v>
       </c>
       <c r="U17">
-        <v>0.058</v>
+        <v>0.004</v>
       </c>
       <c r="V17">
-        <v>0.3036649214659686</v>
+        <v>0.0144927536231884</v>
       </c>
       <c r="W17">
-        <v>-0.002604166666666667</v>
+        <v>0.1351351351351351</v>
       </c>
       <c r="X17">
-        <v>0.07210301598726665</v>
+        <v>0.1599595004619053</v>
       </c>
       <c r="Y17">
-        <v>-0.07470718265393332</v>
+        <v>-0.02482436532677013</v>
       </c>
       <c r="Z17">
-        <v>0.06663084363245567</v>
+        <v>0.2648456057007126</v>
       </c>
       <c r="AA17">
-        <v>-0.01773240193444385</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>0.07709484847323424</v>
+        <v>0.1325306131853274</v>
       </c>
       <c r="AC17">
-        <v>-0.09482725040767809</v>
+        <v>-0.1325306131853274</v>
       </c>
       <c r="AD17">
-        <v>0.032</v>
+        <v>0.634</v>
       </c>
       <c r="AE17">
         <v>0</v>
       </c>
       <c r="AF17">
-        <v>0.032</v>
+        <v>0.634</v>
       </c>
       <c r="AG17">
-        <v>-0.026</v>
+        <v>0.63</v>
       </c>
       <c r="AH17">
-        <v>0.1434977578475336</v>
+        <v>0.6967032967032967</v>
       </c>
       <c r="AI17">
-        <v>0.02219140083217753</v>
+        <v>0.9476831091180866</v>
       </c>
       <c r="AJ17">
-        <v>-0.1575757575757576</v>
+        <v>0.695364238410596</v>
       </c>
       <c r="AK17">
-        <v>-0.01878612716763006</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="AL17">
         <v>0</v>
       </c>
       <c r="AM17">
         <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>-1.066666666666667</v>
-      </c>
-      <c r="AP17">
-        <v>0.8666666666666668</v>
       </c>
     </row>
     <row r="18">
@@ -2615,28 +2597,25 @@
         </is>
       </c>
       <c r="D18">
-        <v>0.12</v>
-      </c>
-      <c r="E18">
-        <v>0.8120000000000001</v>
+        <v>0.07049999999999999</v>
       </c>
       <c r="G18">
-        <v>0.3193069306930693</v>
+        <v>-0.01206030150753769</v>
       </c>
       <c r="H18">
-        <v>0.3193069306930693</v>
+        <v>-0.01206030150753769</v>
       </c>
       <c r="I18">
-        <v>0.1881188118811881</v>
+        <v>-0.02160804020100502</v>
       </c>
       <c r="J18">
-        <v>0.1245091458298372</v>
+        <v>-0.02160804020100502</v>
       </c>
       <c r="K18">
-        <v>0.515</v>
+        <v>-0.414</v>
       </c>
       <c r="L18">
-        <v>0.1274752475247525</v>
+        <v>-0.2080402010050251</v>
       </c>
       <c r="M18">
         <v>-0</v>
@@ -2645,7 +2624,7 @@
         <v>-0</v>
       </c>
       <c r="O18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P18">
         <v>-0</v>
@@ -2654,79 +2633,79 @@
         <v>-0</v>
       </c>
       <c r="R18">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>0.146</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="W18">
-        <v>0.06830238726790451</v>
+        <v>-0.05267175572519083</v>
       </c>
       <c r="X18">
-        <v>0.2139115332519218</v>
+        <v>0.3177600892988718</v>
       </c>
       <c r="Y18">
-        <v>-0.1456091459840173</v>
+        <v>-0.3704318450240626</v>
       </c>
       <c r="Z18">
-        <v>0.1665910684095502</v>
+        <v>0.09031086907193102</v>
       </c>
       <c r="AA18">
-        <v>0.02074211163055307</v>
+        <v>-0.001951440889493987</v>
       </c>
       <c r="AB18">
-        <v>0.1181186588284905</v>
+        <v>0.1386212578897194</v>
       </c>
       <c r="AC18">
-        <v>-0.09737654719793747</v>
+        <v>-0.1405726987792133</v>
       </c>
       <c r="AD18">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="AE18">
         <v>0</v>
       </c>
       <c r="AF18">
-        <v>13</v>
+        <v>10.4</v>
       </c>
       <c r="AG18">
-        <v>13</v>
+        <v>10.254</v>
       </c>
       <c r="AH18">
-        <v>0.873069173942243</v>
+        <v>0.8768971332209107</v>
       </c>
       <c r="AI18">
-        <v>0.6103286384976525</v>
+        <v>0.5953062392673154</v>
       </c>
       <c r="AJ18">
-        <v>0.873069173942243</v>
+        <v>0.8753628137271642</v>
       </c>
       <c r="AK18">
-        <v>0.6103286384976525</v>
+        <v>0.5918956361117526</v>
       </c>
       <c r="AL18">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AM18">
-        <v>1.084</v>
+        <v>0.93</v>
       </c>
       <c r="AN18">
-        <v>16.62404092071611</v>
+        <v>-433.3333333333333</v>
       </c>
       <c r="AO18">
-        <v>0.5629629629629629</v>
+        <v>-0.03257575757575757</v>
       </c>
       <c r="AP18">
-        <v>16.62404092071611</v>
+        <v>-427.25</v>
       </c>
       <c r="AQ18">
-        <v>0.7011070110701106</v>
+        <v>-0.04623655913978494</v>
       </c>
     </row>
     <row r="19">
@@ -2737,7 +2716,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>First Dawood Investment Bank Limited (KASE:FDIBL)</t>
+          <t>First Elite Capital Modaraba (KASE:FECM)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2746,25 +2725,25 @@
         </is>
       </c>
       <c r="D19">
-        <v>0.126</v>
+        <v>-0.05139999999999999</v>
       </c>
       <c r="G19">
-        <v>0</v>
+        <v>-0.1721311475409836</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>-0.1721311475409836</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>-0.1639344262295082</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>-0.1639344262295082</v>
       </c>
       <c r="K19">
-        <v>-0.171</v>
+        <v>-0.022</v>
       </c>
       <c r="L19">
-        <v>-0.5606557377049181</v>
+        <v>-0.180327868852459</v>
       </c>
       <c r="M19">
         <v>-0</v>
@@ -2788,55 +2767,55 @@
         <v>0</v>
       </c>
       <c r="U19">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="V19">
-        <v>0.01101694915254237</v>
+        <v>0.04739336492890996</v>
       </c>
       <c r="W19">
-        <v>-0.05044247787610619</v>
+        <v>-0.05152224824355971</v>
       </c>
       <c r="X19">
-        <v>0.09381300117228075</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="Y19">
-        <v>-0.144255479048387</v>
+        <v>-0.1363740042788778</v>
       </c>
       <c r="Z19">
-        <v>0.05638750231096321</v>
+        <v>0.4535315985130111</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>-0.07434944237918216</v>
       </c>
       <c r="AB19">
-        <v>0.09946326175402483</v>
+        <v>0.08485175603531805</v>
       </c>
       <c r="AC19">
-        <v>-0.09946326175402483</v>
+        <v>-0.1592011984145002</v>
       </c>
       <c r="AD19">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AE19">
         <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.397</v>
+        <v>-0.01</v>
       </c>
       <c r="AH19">
-        <v>0.5444015444015444</v>
+        <v>0</v>
       </c>
       <c r="AI19">
-        <v>0.3700787401574803</v>
+        <v>0</v>
       </c>
       <c r="AJ19">
-        <v>0.5421032207993791</v>
+        <v>-0.04975124378109453</v>
       </c>
       <c r="AK19">
-        <v>0.3679220437187253</v>
+        <v>-0.03194888178913738</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -2844,490 +2823,11 @@
       <c r="AM19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>OLP Financial Services Pakistan Limited (KASE:OLPL)</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>-0.013</v>
-      </c>
-      <c r="E20">
-        <v>0.027</v>
-      </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20">
-        <v>0</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>3.97</v>
-      </c>
-      <c r="L20">
-        <v>0.2294797687861272</v>
-      </c>
-      <c r="M20">
-        <v>2.81</v>
-      </c>
-      <c r="N20">
-        <v>0.1860927152317881</v>
-      </c>
-      <c r="O20">
-        <v>0.707808564231738</v>
-      </c>
-      <c r="P20">
-        <v>2.81</v>
-      </c>
-      <c r="Q20">
-        <v>0.1860927152317881</v>
-      </c>
-      <c r="R20">
-        <v>0.707808564231738</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>4.22</v>
-      </c>
-      <c r="V20">
-        <v>0.2794701986754967</v>
-      </c>
-      <c r="W20">
-        <v>0.07738791423001951</v>
-      </c>
-      <c r="X20">
-        <v>0.1402138058672352</v>
-      </c>
-      <c r="Y20">
-        <v>-0.06282589163721569</v>
-      </c>
-      <c r="Z20">
-        <v>0.1318999695028972</v>
-      </c>
-      <c r="AA20">
-        <v>0</v>
-      </c>
-      <c r="AB20">
-        <v>0.1081740681468557</v>
-      </c>
-      <c r="AC20">
-        <v>-0.1081740681468557</v>
-      </c>
-      <c r="AD20">
-        <v>51.2</v>
-      </c>
-      <c r="AE20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>51.2</v>
-      </c>
-      <c r="AG20">
-        <v>46.98</v>
-      </c>
-      <c r="AH20">
-        <v>0.7722473604826546</v>
-      </c>
-      <c r="AI20">
-        <v>0.5372507869884575</v>
-      </c>
-      <c r="AJ20">
-        <v>0.7567654639175257</v>
-      </c>
-      <c r="AK20">
-        <v>0.5158102766798419</v>
-      </c>
-      <c r="AL20">
-        <v>0</v>
-      </c>
-      <c r="AM20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>First Paramount Modaraba (KASE:FPRM)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>0.00176</v>
-      </c>
-      <c r="E21">
-        <v>-0.05230000000000001</v>
-      </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>0.023</v>
-      </c>
-      <c r="L21">
-        <v>0.02486486486486486</v>
-      </c>
-      <c r="M21">
-        <v>0.021</v>
-      </c>
-      <c r="N21">
-        <v>0.05801104972375691</v>
-      </c>
-      <c r="O21">
-        <v>0.9130434782608696</v>
-      </c>
-      <c r="P21">
-        <v>0.021</v>
-      </c>
-      <c r="Q21">
-        <v>0.05801104972375691</v>
-      </c>
-      <c r="R21">
-        <v>0.9130434782608696</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0.414</v>
-      </c>
-      <c r="V21">
-        <v>1.143646408839779</v>
-      </c>
-      <c r="W21">
-        <v>0.01854838709677419</v>
-      </c>
-      <c r="X21">
-        <v>0.1145032209728087</v>
-      </c>
-      <c r="Y21">
-        <v>-0.09595483387603454</v>
-      </c>
-      <c r="Z21">
-        <v>0.4357041921808761</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0.1092884916093379</v>
-      </c>
-      <c r="AC21">
-        <v>-0.1092884916093379</v>
-      </c>
-      <c r="AD21">
-        <v>0.787</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0.787</v>
-      </c>
-      <c r="AG21">
-        <v>0.3730000000000001</v>
-      </c>
-      <c r="AH21">
-        <v>0.6849434290687555</v>
-      </c>
-      <c r="AI21">
-        <v>0.4538638985005767</v>
-      </c>
-      <c r="AJ21">
-        <v>0.507482993197279</v>
-      </c>
-      <c r="AK21">
-        <v>0.2825757575757576</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>SME Leasing Limited (KASE:SLL)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>-0.0515</v>
-      </c>
-      <c r="G22">
-        <v>0</v>
-      </c>
-      <c r="H22">
-        <v>0</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>-0.161</v>
-      </c>
-      <c r="L22">
-        <v>-2.515625</v>
-      </c>
-      <c r="M22">
-        <v>-0</v>
-      </c>
-      <c r="N22">
-        <v>-0</v>
-      </c>
-      <c r="O22">
-        <v>0</v>
-      </c>
-      <c r="P22">
-        <v>-0</v>
-      </c>
-      <c r="Q22">
-        <v>-0</v>
-      </c>
-      <c r="R22">
-        <v>0</v>
-      </c>
-      <c r="S22">
-        <v>0</v>
-      </c>
-      <c r="U22">
-        <v>0.008</v>
-      </c>
-      <c r="V22">
-        <v>0.02826855123674912</v>
-      </c>
-      <c r="W22">
-        <v>-0.9640718562874251</v>
-      </c>
-      <c r="X22">
-        <v>0.1263569129060487</v>
-      </c>
-      <c r="Y22">
-        <v>-1.090428769193474</v>
-      </c>
-      <c r="Z22">
-        <v>0.0557006092254134</v>
-      </c>
-      <c r="AA22">
-        <v>0</v>
-      </c>
-      <c r="AB22">
-        <v>0.1121019386823786</v>
-      </c>
-      <c r="AC22">
-        <v>-0.1121019386823786</v>
-      </c>
-      <c r="AD22">
-        <v>0.774</v>
-      </c>
-      <c r="AE22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>0.774</v>
-      </c>
-      <c r="AG22">
-        <v>0.766</v>
-      </c>
-      <c r="AH22">
-        <v>0.7322611163670767</v>
-      </c>
-      <c r="AI22">
-        <v>1.025165562913907</v>
-      </c>
-      <c r="AJ22">
-        <v>0.7302192564346998</v>
-      </c>
-      <c r="AK22">
-        <v>1.025435073627845</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Pakistan</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>First Elite Capital Modaraba (KASE:FECM)</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>-0.0751</v>
-      </c>
-      <c r="G23">
-        <v>-0.2077922077922078</v>
-      </c>
-      <c r="H23">
-        <v>-0.2077922077922078</v>
-      </c>
-      <c r="I23">
-        <v>-0.1883116883116883</v>
-      </c>
-      <c r="J23">
-        <v>-0.1883116883116883</v>
-      </c>
-      <c r="K23">
-        <v>-0.031</v>
-      </c>
-      <c r="L23">
-        <v>-0.2012987012987013</v>
-      </c>
-      <c r="M23">
-        <v>0.014</v>
-      </c>
-      <c r="N23">
-        <v>0.0903225806451613</v>
-      </c>
-      <c r="O23">
-        <v>-0.4516129032258064</v>
-      </c>
-      <c r="P23">
-        <v>0.014</v>
-      </c>
-      <c r="Q23">
-        <v>0.0903225806451613</v>
-      </c>
-      <c r="R23">
-        <v>-0.4516129032258064</v>
-      </c>
-      <c r="S23">
-        <v>0</v>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="U23">
-        <v>0.158</v>
-      </c>
-      <c r="V23">
-        <v>1.019354838709677</v>
-      </c>
-      <c r="W23">
-        <v>-0.0496</v>
-      </c>
-      <c r="X23">
-        <v>0.06856266167681045</v>
-      </c>
-      <c r="Y23">
-        <v>-0.1181626616768104</v>
-      </c>
-      <c r="Z23">
-        <v>0.318840579710145</v>
-      </c>
-      <c r="AA23">
-        <v>-0.06004140786749483</v>
-      </c>
-      <c r="AB23">
-        <v>0.06856266167681045</v>
-      </c>
-      <c r="AC23">
-        <v>-0.1286040695443053</v>
-      </c>
-      <c r="AD23">
-        <v>0</v>
-      </c>
-      <c r="AE23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>0</v>
-      </c>
-      <c r="AG23">
-        <v>-0.158</v>
-      </c>
-      <c r="AH23">
-        <v>0</v>
-      </c>
-      <c r="AI23">
-        <v>0</v>
-      </c>
-      <c r="AJ23">
-        <v>52.66666666666662</v>
-      </c>
-      <c r="AK23">
-        <v>-0.587360594795539</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>-0</v>
-      </c>
-      <c r="AP23">
-        <v>5.642857142857143</v>
+      <c r="AN19">
+        <v>-0</v>
+      </c>
+      <c r="AP19">
+        <v>0.5263157894736842</v>
       </c>
     </row>
   </sheetData>
